--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -274,7 +274,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,6 +287,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -780,137 +787,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -921,6 +928,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1341,16 +1349,16 @@
       <c r="E6" s="2">
         <v>9</v>
       </c>
-      <c r="F6" s="1">
-        <v>62000001</v>
+      <c r="F6" s="4">
+        <v>2100001</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J6" s="2"/>
@@ -1366,16 +1374,16 @@
       <c r="E7" s="2">
         <v>9</v>
       </c>
-      <c r="F7" s="1">
-        <v>62000002</v>
+      <c r="F7" s="4">
+        <v>2100002</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="2"/>
@@ -1391,16 +1399,16 @@
       <c r="E8" s="2">
         <v>8</v>
       </c>
-      <c r="F8" s="1">
-        <v>62000003</v>
+      <c r="F8" s="4">
+        <v>2100003</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J8" s="1"/>
@@ -1416,16 +1424,16 @@
       <c r="E9" s="2">
         <v>8</v>
       </c>
-      <c r="F9" s="1">
-        <v>62000004</v>
+      <c r="F9" s="4">
+        <v>2100004</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J9" s="1"/>
@@ -1441,16 +1449,16 @@
       <c r="E10" s="2">
         <v>8</v>
       </c>
-      <c r="F10" s="1">
-        <v>62000005</v>
+      <c r="F10" s="4">
+        <v>2100005</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J10" s="1"/>
@@ -1466,16 +1474,16 @@
       <c r="E11" s="2">
         <v>7</v>
       </c>
-      <c r="F11" s="1">
-        <v>62000006</v>
+      <c r="F11" s="4">
+        <v>2100006</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J11" s="1"/>
@@ -1491,16 +1499,16 @@
       <c r="E12" s="2">
         <v>7</v>
       </c>
-      <c r="F12" s="1">
-        <v>62000007</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="4">
+        <v>2100007</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L12" s="2"/>
@@ -1515,16 +1523,16 @@
       <c r="E13" s="2">
         <v>7</v>
       </c>
-      <c r="F13" s="1">
-        <v>62000008</v>
+      <c r="F13" s="4">
+        <v>2100008</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L13" s="2"/>
@@ -1539,16 +1547,16 @@
       <c r="E14" s="2">
         <v>6</v>
       </c>
-      <c r="F14" s="1">
-        <v>62000009</v>
+      <c r="F14" s="4">
+        <v>2100009</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L14" s="2"/>
@@ -1563,16 +1571,16 @@
       <c r="E15" s="2">
         <v>6</v>
       </c>
-      <c r="F15" s="1">
-        <v>62000010</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="4">
+        <v>2100010</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L15" s="2"/>
@@ -1587,16 +1595,16 @@
       <c r="E16" s="2">
         <v>6</v>
       </c>
-      <c r="F16" s="1">
-        <v>62000011</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="F16" s="4">
+        <v>2100011</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J16" s="1"/>
@@ -1612,16 +1620,16 @@
       <c r="E17" s="2">
         <v>5</v>
       </c>
-      <c r="F17" s="1">
-        <v>62000012</v>
+      <c r="F17" s="4">
+        <v>2100012</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="9" t="s">
         <v>14</v>
       </c>
       <c r="M17" s="1"/>
@@ -1638,16 +1646,16 @@
       <c r="E18" s="2">
         <v>5</v>
       </c>
-      <c r="F18" s="1">
-        <v>62000013</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="F18" s="4">
+        <v>2100013</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L18" s="2"/>
@@ -1662,16 +1670,16 @@
       <c r="E19" s="2">
         <v>5</v>
       </c>
-      <c r="F19" s="1">
-        <v>62000014</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="4">
+        <v>2100014</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J19" s="2"/>
@@ -1687,16 +1695,16 @@
       <c r="E20" s="2">
         <v>4</v>
       </c>
-      <c r="F20" s="1">
-        <v>62000015</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="4">
+        <v>2100015</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J20" s="2"/>
@@ -1714,16 +1722,16 @@
       <c r="E21" s="2">
         <v>4</v>
       </c>
-      <c r="F21" s="1">
-        <v>62000016</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F21" s="4">
+        <v>2100016</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J21" s="1"/>
@@ -1741,16 +1749,16 @@
       <c r="E22" s="2">
         <v>4</v>
       </c>
-      <c r="F22" s="1">
-        <v>62000017</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="F22" s="4">
+        <v>2100017</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L22" s="2"/>
@@ -1765,16 +1773,16 @@
       <c r="E23" s="2">
         <v>4</v>
       </c>
-      <c r="F23" s="1">
-        <v>62000018</v>
+      <c r="F23" s="4">
+        <v>2100018</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J23" s="1"/>
@@ -1793,16 +1801,16 @@
       <c r="E24" s="2">
         <v>3</v>
       </c>
-      <c r="F24" s="1">
-        <v>62000019</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="F24" s="4">
+        <v>2100019</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L24" s="2"/>
@@ -1817,16 +1825,16 @@
       <c r="E25" s="2">
         <v>3</v>
       </c>
-      <c r="F25" s="1">
-        <v>62000020</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="4">
+        <v>2100020</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L25" s="2"/>
@@ -1841,16 +1849,16 @@
       <c r="E26" s="2">
         <v>3</v>
       </c>
-      <c r="F26" s="1">
-        <v>62000021</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="F26" s="4">
+        <v>2100021</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L26" s="2"/>
@@ -1865,16 +1873,16 @@
       <c r="E27" s="2">
         <v>3</v>
       </c>
-      <c r="F27" s="1">
-        <v>62000022</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="F27" s="4">
+        <v>2100022</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L27" s="2"/>
@@ -1889,16 +1897,16 @@
       <c r="E28" s="2">
         <v>2</v>
       </c>
-      <c r="F28" s="1">
-        <v>62000023</v>
-      </c>
-      <c r="G28" s="7" t="s">
+      <c r="F28" s="4">
+        <v>2100023</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L28" s="2"/>
@@ -1913,16 +1921,16 @@
       <c r="E29" s="2">
         <v>2</v>
       </c>
-      <c r="F29" s="1">
-        <v>62000024</v>
+      <c r="F29" s="4">
+        <v>2100024</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L29" s="2"/>
@@ -1937,16 +1945,16 @@
       <c r="E30" s="2">
         <v>2</v>
       </c>
-      <c r="F30" s="1">
-        <v>62000025</v>
-      </c>
-      <c r="G30" s="7" t="s">
+      <c r="F30" s="4">
+        <v>2100025</v>
+      </c>
+      <c r="G30" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L30" s="2"/>
@@ -1961,16 +1969,16 @@
       <c r="E31" s="2">
         <v>2</v>
       </c>
-      <c r="F31" s="1">
-        <v>62000026</v>
+      <c r="F31" s="4">
+        <v>2100026</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="9" t="s">
         <v>14</v>
       </c>
       <c r="L31" s="2"/>
@@ -1985,7 +1993,7 @@
     <row r="33" customHeight="1" spans="3:12">
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="G33" s="6"/>
+      <c r="G33" s="7"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="L33" s="2"/>
@@ -2054,7 +2062,7 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="G42" s="6"/>
+      <c r="G42" s="7"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="L42" s="2"/>
@@ -2122,7 +2130,7 @@
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="G51" s="6"/>
+      <c r="G51" s="7"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="L51" s="2"/>

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>#</t>
   </si>
@@ -65,110 +65,79 @@
     <t>double[]</t>
   </si>
   <si>
+    <t>关羽</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2013,2004,2007,91,95</t>
+  </si>
+  <si>
+    <t>3,3,3,3,3,3,0.2,3</t>
+  </si>
+  <si>
     <t>刘备</t>
   </si>
   <si>
-    <t>2001,2002,2003,2004</t>
-  </si>
-  <si>
-    <t>10,15,20,10</t>
+    <t>2001,2003,2010,2013,2005,2008,92,95</t>
   </si>
   <si>
     <t>诸葛亮</t>
   </si>
   <si>
-    <t>2001,2002,2003,2005</t>
-  </si>
-  <si>
-    <t>关羽</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2006</t>
+    <t>2001,2003,2010,2013,2006,2009,93,95</t>
   </si>
   <si>
     <t>赵云</t>
   </si>
   <si>
-    <t>2001,2002,2003,2007</t>
+    <t>2.6,2.6,2.6,2.6,2.6,2.6,0.1,2.6</t>
   </si>
   <si>
     <t>张飞</t>
   </si>
   <si>
-    <t>2001,2002,2003,2008</t>
+    <t>马超</t>
+  </si>
+  <si>
+    <t>魏延</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2013,2007,91,95</t>
+  </si>
+  <si>
+    <t>2.4,2.4,2.4,2.4,2.4,0.1,2.4</t>
   </si>
   <si>
     <t>黄忠</t>
   </si>
   <si>
-    <t>2001,2002,2003,2009</t>
-  </si>
-  <si>
-    <t>马超</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2010</t>
-  </si>
-  <si>
-    <t>魏延</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2012</t>
+    <t>2001,2003,2010,2013,2007,92,95</t>
+  </si>
+  <si>
+    <t>黄月英</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2013,2007,93,95</t>
   </si>
   <si>
     <t>关银屏</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>黄月英</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>马云禄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
+    <t>2,2,2,2,2,0.1,2</t>
+  </si>
+  <si>
+    <t>张星彩</t>
+  </si>
+  <si>
+    <t>马云禄</t>
   </si>
   <si>
     <t>庞统</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2013,2007,95</t>
+  </si>
+  <si>
+    <t>1.8,1.8,1.8,1.8,1.8,1.8</t>
   </si>
   <si>
     <r>
@@ -191,10 +160,19 @@
     </r>
   </si>
   <si>
+    <t>2001,2003,2010,2013,2008,95</t>
+  </si>
+  <si>
     <t>严颜</t>
   </si>
   <si>
+    <t>2001,2003,2010,2013,2009,95</t>
+  </si>
+  <si>
     <t>伊籍</t>
+  </si>
+  <si>
+    <t>1.6,1.6,1.6,1.6,1.6,1.6</t>
   </si>
   <si>
     <t>徐庶</t>
@@ -223,10 +201,22 @@
     <t>关平</t>
   </si>
   <si>
+    <t>2001,2003,2013,2007,95</t>
+  </si>
+  <si>
+    <t>1.4,1.4,1.4,1.4,1.4</t>
+  </si>
+  <si>
     <t>张兴</t>
   </si>
   <si>
+    <t>2001,2003,2013,2008,95</t>
+  </si>
+  <si>
     <t>陈到</t>
+  </si>
+  <si>
+    <t>2001,2003,2013,2009,95</t>
   </si>
   <si>
     <r>
@@ -249,6 +239,9 @@
     </r>
   </si>
   <si>
+    <t>1.2,1.2,1.2,1.2,1.2</t>
+  </si>
+  <si>
     <t>张苞</t>
   </si>
   <si>
@@ -256,6 +249,12 @@
   </si>
   <si>
     <t>廖化</t>
+  </si>
+  <si>
+    <t>2001,2003,2013,95</t>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
   </si>
   <si>
     <t>周仓</t>
@@ -1249,13 +1248,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
     <col min="6" max="6" width="9.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5833333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="17.75" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
@@ -1389,18 +1388,18 @@
       <c r="J7" s="2"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C8" s="1">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="4">
-        <v>2100003</v>
+        <v>2100002</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1411,11 +1410,10 @@
       <c r="I8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
-      <c r="C9" s="1">
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2">
@@ -1425,22 +1423,21 @@
         <v>8</v>
       </c>
       <c r="F9" s="4">
-        <v>2100004</v>
+        <v>2100003</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="1"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C10" s="1">
+    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="2">
@@ -1450,47 +1447,47 @@
         <v>8</v>
       </c>
       <c r="F10" s="4">
-        <v>2100005</v>
+        <v>2100004</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J10" s="1"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>6</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4">
-        <v>2100006</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>23</v>
+        <v>2100005</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J11" s="1"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" customHeight="1" spans="3:13">
-      <c r="C12" s="1">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C12" s="2">
         <v>7</v>
       </c>
       <c r="D12" s="2">
@@ -1500,21 +1497,22 @@
         <v>7</v>
       </c>
       <c r="F12" s="4">
-        <v>2100007</v>
-      </c>
-      <c r="G12" s="5" t="s">
+        <v>2100006</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>14</v>
-      </c>
+      <c r="J12" s="1"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>8</v>
       </c>
       <c r="D13" s="2">
@@ -1524,45 +1522,45 @@
         <v>7</v>
       </c>
       <c r="F13" s="4">
+        <v>2100007</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:13">
+      <c r="C14" s="2">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4">
         <v>2100008</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="9" t="s">
+      <c r="G14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2">
-        <v>6</v>
-      </c>
-      <c r="F14" s="4">
-        <v>2100009</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>28</v>
-      </c>
       <c r="I14" s="9" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>10</v>
       </c>
       <c r="D15" s="2">
@@ -1572,21 +1570,21 @@
         <v>6</v>
       </c>
       <c r="F15" s="4">
-        <v>2100010</v>
-      </c>
-      <c r="G15" s="6" t="s">
+        <v>2100009</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C16" s="1">
+    <row r="16" customHeight="1" spans="3:13">
+      <c r="C16" s="2">
         <v>11</v>
       </c>
       <c r="D16" s="2">
@@ -1596,48 +1594,46 @@
         <v>6</v>
       </c>
       <c r="F16" s="4">
+        <v>2100010</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>6</v>
+      </c>
+      <c r="F17" s="4">
         <v>2100011</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2">
-        <v>5</v>
-      </c>
-      <c r="F17" s="4">
-        <v>2100012</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="M17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:13">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="1">
+      <c r="J17" s="1"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C18" s="2">
         <v>13</v>
       </c>
       <c r="D18" s="2">
@@ -1647,21 +1643,23 @@
         <v>5</v>
       </c>
       <c r="F18" s="4">
-        <v>2100013</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>33</v>
+        <v>2100012</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C19" s="1">
+        <v>36</v>
+      </c>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:13">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2">
         <v>14</v>
       </c>
       <c r="D19" s="2">
@@ -1671,49 +1669,46 @@
         <v>5</v>
       </c>
       <c r="F19" s="4">
+        <v>2100013</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C20" s="2">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4">
         <v>2100014</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="2"/>
-      <c r="M19" s="1"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4</v>
-      </c>
-      <c r="F20" s="4">
-        <v>2100015</v>
-      </c>
       <c r="G20" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="J20" s="2"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="1">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C21" s="2">
         <v>16</v>
       </c>
       <c r="D21" s="2">
@@ -1723,24 +1718,24 @@
         <v>4</v>
       </c>
       <c r="F21" s="4">
-        <v>2100016</v>
+        <v>2100015</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="1"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:13">
+        <v>42</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="M21" s="1"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="1">
+      <c r="C22" s="2">
         <v>17</v>
       </c>
       <c r="D22" s="2">
@@ -1750,21 +1745,24 @@
         <v>4</v>
       </c>
       <c r="F22" s="4">
-        <v>2100017</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>37</v>
+        <v>2100016</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>14</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J22" s="1"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C23" s="1">
+    <row r="23" customHeight="1" spans="1:13">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2">
         <v>18</v>
       </c>
       <c r="D23" s="2">
@@ -1774,25 +1772,21 @@
         <v>4</v>
       </c>
       <c r="F23" s="4">
-        <v>2100018</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>38</v>
+        <v>2100017</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="M23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:13">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="1">
+        <v>42</v>
+      </c>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C24" s="2">
         <v>19</v>
       </c>
       <c r="D24" s="2">
@@ -1802,21 +1796,25 @@
         <v>3</v>
       </c>
       <c r="F24" s="4">
-        <v>2100019</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>39</v>
+        <v>2100018</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="M24" s="1"/>
     </row>
     <row r="25" customHeight="1" spans="1:13">
-      <c r="C25" s="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2">
         <v>20</v>
       </c>
       <c r="D25" s="2">
@@ -1826,21 +1824,21 @@
         <v>3</v>
       </c>
       <c r="F25" s="4">
-        <v>2100020</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>40</v>
+        <v>2100019</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="L25" s="2"/>
     </row>
     <row r="26" customHeight="1" spans="1:13">
-      <c r="C26" s="1">
+      <c r="C26" s="2">
         <v>21</v>
       </c>
       <c r="D26" s="2">
@@ -1850,45 +1848,45 @@
         <v>3</v>
       </c>
       <c r="F26" s="4">
+        <v>2100020</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:13">
+      <c r="C27" s="2">
+        <v>22</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
+      </c>
+      <c r="F27" s="4">
         <v>2100021</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:13">
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1</v>
-      </c>
-      <c r="E27" s="2">
-        <v>3</v>
-      </c>
-      <c r="F27" s="4">
-        <v>2100022</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>42</v>
+      <c r="G27" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="L27" s="2"/>
     </row>
     <row r="28" customHeight="1" spans="1:13">
-      <c r="C28" s="1">
+      <c r="C28" s="2">
         <v>23</v>
       </c>
       <c r="D28" s="2">
@@ -1898,21 +1896,21 @@
         <v>2</v>
       </c>
       <c r="F28" s="4">
-        <v>2100023</v>
+        <v>2100022</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="L28" s="2"/>
     </row>
     <row r="29" customHeight="1" spans="1:13">
-      <c r="C29" s="1">
+      <c r="C29" s="2">
         <v>24</v>
       </c>
       <c r="D29" s="2">
@@ -1922,78 +1920,94 @@
         <v>2</v>
       </c>
       <c r="F29" s="4">
+        <v>2100023</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:13">
+      <c r="C30" s="2">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4">
         <v>2100024</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:13">
-      <c r="C30" s="1">
-        <v>25</v>
-      </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2">
-        <v>2</v>
-      </c>
-      <c r="F30" s="4">
+      <c r="G30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:13">
+      <c r="C31" s="2">
+        <v>26</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4">
         <v>2100025</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:13">
-      <c r="C31" s="1">
-        <v>26</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2</v>
-      </c>
-      <c r="F31" s="4">
+      <c r="G31" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:13">
+      <c r="C32" s="2">
+        <v>27</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4">
         <v>2100026</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:13">
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="G32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="L32" s="2"/>
     </row>
     <row r="33" customHeight="1" spans="3:12">
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="G33" s="7"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="L33" s="2"/>
@@ -2001,17 +2015,17 @@
     <row r="34" customHeight="1" spans="3:12">
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" customHeight="1" spans="3:12">
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
       <c r="L35" s="2"/>
     </row>
     <row r="36" customHeight="1" spans="3:12">
-      <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="H36" s="2"/>
@@ -2062,20 +2076,20 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="G42" s="7"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" customHeight="1" spans="3:12">
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
       <c r="L43" s="2"/>
     </row>
     <row r="44" customHeight="1" spans="3:12">
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
       <c r="L44" s="2"/>
     </row>
     <row r="45" customHeight="1" spans="3:12">
@@ -2130,12 +2144,17 @@
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="G51" s="7"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="L51" s="2"/>
     </row>
     <row r="52" customHeight="1" spans="3:12">
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
       <c r="L52" s="2"/>
     </row>
     <row r="53" customHeight="1" spans="3:12">
@@ -2146,6 +2165,9 @@
     </row>
     <row r="55" customHeight="1" spans="3:12">
       <c r="L55" s="2"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:12">
+      <c r="L56" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -89,7 +89,7 @@
     <t>赵云</t>
   </si>
   <si>
-    <t>2.6,2.6,2.6,2.6,2.6,2.6,0.1,2.6</t>
+    <t>2.6,2.6,2.6,2.6,2.6,2.6,0.1,2</t>
   </si>
   <si>
     <t>张飞</t>
@@ -104,7 +104,7 @@
     <t>2001,2003,2010,2013,2007,91,95</t>
   </si>
   <si>
-    <t>2.4,2.4,2.4,2.4,2.4,0.1,2.4</t>
+    <t>2.4,2.4,2.4,2.4,2.4,0.1,1.5</t>
   </si>
   <si>
     <t>黄忠</t>
@@ -122,7 +122,7 @@
     <t>关银屏</t>
   </si>
   <si>
-    <t>2,2,2,2,2,0.1,2</t>
+    <t>2,2,2,2,2,0.1,1.2</t>
   </si>
   <si>
     <t>张星彩</t>
@@ -137,7 +137,7 @@
     <t>2001,2003,2010,2013,2007,95</t>
   </si>
   <si>
-    <t>1.8,1.8,1.8,1.8,1.8,1.8</t>
+    <t>1.8,1.8,1.8,1.8,1.8,1</t>
   </si>
   <si>
     <r>
@@ -172,7 +172,7 @@
     <t>伊籍</t>
   </si>
   <si>
-    <t>1.6,1.6,1.6,1.6,1.6,1.6</t>
+    <t>1.6,1.6,1.6,1.6,1.6,0.8</t>
   </si>
   <si>
     <t>徐庶</t>
@@ -204,7 +204,7 @@
     <t>2001,2003,2013,2007,95</t>
   </si>
   <si>
-    <t>1.4,1.4,1.4,1.4,1.4</t>
+    <t>1.4,1.4,1.4,1.4,0.5</t>
   </si>
   <si>
     <t>张兴</t>
@@ -239,7 +239,7 @@
     </r>
   </si>
   <si>
-    <t>1.2,1.2,1.2,1.2,1.2</t>
+    <t>1.2,1.2,1.2,1.2,0.3</t>
   </si>
   <si>
     <t>张苞</t>
@@ -254,7 +254,7 @@
     <t>2001,2003,2013,95</t>
   </si>
   <si>
-    <t>1,1,1,1</t>
+    <t>1,1,1,0.1</t>
   </si>
   <si>
     <t>周仓</t>
@@ -1399,7 +1399,7 @@
         <v>9</v>
       </c>
       <c r="F8" s="4">
-        <v>2100002</v>
+        <v>2100003</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1423,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="4">
-        <v>2100003</v>
+        <v>2100004</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>19</v>
@@ -1447,7 +1447,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="4">
-        <v>2100004</v>
+        <v>2100005</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>21</v>
@@ -1472,7 +1472,7 @@
         <v>8</v>
       </c>
       <c r="F11" s="4">
-        <v>2100005</v>
+        <v>2100006</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>22</v>
@@ -1497,7 +1497,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="4">
-        <v>2100006</v>
+        <v>2100007</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>23</v>
@@ -1522,7 +1522,7 @@
         <v>7</v>
       </c>
       <c r="F13" s="4">
-        <v>2100007</v>
+        <v>2100008</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>26</v>
@@ -1546,7 +1546,7 @@
         <v>7</v>
       </c>
       <c r="F14" s="4">
-        <v>2100008</v>
+        <v>2100009</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>28</v>
@@ -1570,7 +1570,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="4">
-        <v>2100009</v>
+        <v>2100010</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>30</v>
@@ -1594,7 +1594,7 @@
         <v>6</v>
       </c>
       <c r="F16" s="4">
-        <v>2100010</v>
+        <v>2100011</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>32</v>
@@ -1618,7 +1618,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="4">
-        <v>2100011</v>
+        <v>2100012</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>33</v>
@@ -1643,7 +1643,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="4">
-        <v>2100012</v>
+        <v>2100013</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>34</v>
@@ -1669,7 +1669,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="4">
-        <v>2100013</v>
+        <v>2100014</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>37</v>
@@ -1693,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="4">
-        <v>2100014</v>
+        <v>2100015</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>39</v>
@@ -1718,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="4">
-        <v>2100015</v>
+        <v>2100016</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>41</v>
@@ -1745,7 +1745,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="4">
-        <v>2100016</v>
+        <v>2100017</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>43</v>
@@ -1772,7 +1772,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="4">
-        <v>2100017</v>
+        <v>2100018</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>44</v>
@@ -1796,7 +1796,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="4">
-        <v>2100018</v>
+        <v>2100019</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>45</v>
@@ -1824,7 +1824,7 @@
         <v>3</v>
       </c>
       <c r="F25" s="4">
-        <v>2100019</v>
+        <v>2100020</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>48</v>
@@ -1848,7 +1848,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="4">
-        <v>2100020</v>
+        <v>2100021</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>50</v>
@@ -1872,7 +1872,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="4">
-        <v>2100021</v>
+        <v>2100022</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>52</v>
@@ -1896,7 +1896,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="4">
-        <v>2100022</v>
+        <v>2100023</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>54</v>
@@ -1920,7 +1920,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="4">
-        <v>2100023</v>
+        <v>2100024</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>55</v>
@@ -1944,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="4">
-        <v>2100024</v>
+        <v>2100025</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>56</v>
@@ -1968,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="4">
-        <v>2100025</v>
+        <v>2100026</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>59</v>
@@ -1992,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="4">
-        <v>2100026</v>
+        <v>2100027</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>60</v>

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -71,7 +71,7 @@
     <t>2001,2003,2010,2013,2004,2007,91,95</t>
   </si>
   <si>
-    <t>3,3,3,3,3,3,0.2,3</t>
+    <t>3,3,3,3,3,3,0.3,3</t>
   </si>
   <si>
     <t>刘备</t>
@@ -89,7 +89,7 @@
     <t>赵云</t>
   </si>
   <si>
-    <t>2.6,2.6,2.6,2.6,2.6,2.6,0.1,2</t>
+    <t>2.5,2.5,2.5,2.5,2.5,2.5,0.2,2</t>
   </si>
   <si>
     <t>张飞</t>
@@ -104,7 +104,7 @@
     <t>2001,2003,2010,2013,2007,91,95</t>
   </si>
   <si>
-    <t>2.4,2.4,2.4,2.4,2.4,0.1,1.5</t>
+    <t>2,2,2,2,2,0.1,1.5</t>
   </si>
   <si>
     <t>黄忠</t>
@@ -122,7 +122,7 @@
     <t>关银屏</t>
   </si>
   <si>
-    <t>2,2,2,2,2,0.1,1.2</t>
+    <t>1.5,1.5,1.5,1.5,1.5,0.1,1.2</t>
   </si>
   <si>
     <t>张星彩</t>
@@ -134,10 +134,10 @@
     <t>庞统</t>
   </si>
   <si>
-    <t>2001,2003,2010,2013,2007,95</t>
-  </si>
-  <si>
-    <t>1.8,1.8,1.8,1.8,1.8,1</t>
+    <t>2001,2003,2010,2013,91,95</t>
+  </si>
+  <si>
+    <t>1.4,1.4,1.4,1.4,0.1,1</t>
   </si>
   <si>
     <r>
@@ -160,54 +160,37 @@
     </r>
   </si>
   <si>
-    <t>2001,2003,2010,2013,2008,95</t>
+    <t>2001,2003,2010,2013,92,95</t>
   </si>
   <si>
     <t>严颜</t>
   </si>
   <si>
-    <t>2001,2003,2010,2013,2009,95</t>
+    <t>2001,2003,2010,2013,93,95</t>
   </si>
   <si>
     <t>伊籍</t>
   </si>
   <si>
-    <t>1.6,1.6,1.6,1.6,1.6,0.8</t>
+    <t>1.3,1.3,1.3,1.3,0.1,0.8</t>
   </si>
   <si>
     <t>徐庶</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>王平</t>
-    </r>
-  </si>
-  <si>
     <t>关平</t>
   </si>
   <si>
+    <t>张兴</t>
+  </si>
+  <si>
     <t>2001,2003,2013,2007,95</t>
   </si>
   <si>
-    <t>1.4,1.4,1.4,1.4,0.5</t>
-  </si>
-  <si>
-    <t>张兴</t>
+    <t>1.2,1.2,1.2,1.2,0.5</t>
+  </si>
+  <si>
+    <t>王平</t>
   </si>
   <si>
     <t>2001,2003,2013,2008,95</t>
@@ -239,7 +222,7 @@
     </r>
   </si>
   <si>
-    <t>1.2,1.2,1.2,1.2,0.3</t>
+    <t>1.1,1.1,1.1,1.1,0.3</t>
   </si>
   <si>
     <t>张苞</t>
@@ -1774,7 +1757,7 @@
       <c r="F23" s="4">
         <v>2100018</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H23" s="9" t="s">
@@ -1798,7 +1781,7 @@
       <c r="F24" s="4">
         <v>2100019</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="7" t="s">
         <v>45</v>
       </c>
       <c r="H24" s="9" t="s">
@@ -1826,7 +1809,7 @@
       <c r="F25" s="4">
         <v>2100020</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H25" s="9" t="s">

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="69">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +41,9 @@
     <t>Quality</t>
   </si>
   <si>
+    <t>MaxLevel</t>
+  </si>
+  <si>
     <t>ItemId</t>
   </si>
   <si>
@@ -51,6 +54,27 @@
   </si>
   <si>
     <t>AttrValueList</t>
+  </si>
+  <si>
+    <t>19:30开始测试掉落</t>
+  </si>
+  <si>
+    <t xml:space="preserve">橙色 </t>
+  </si>
+  <si>
+    <t>紫色</t>
+  </si>
+  <si>
+    <t>蓝色</t>
+  </si>
+  <si>
+    <t>绿色</t>
+  </si>
+  <si>
+    <t>白色</t>
+  </si>
+  <si>
+    <t>9:30结束</t>
   </si>
   <si>
     <t>int</t>
@@ -1231,28 +1255,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="9.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.5833333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.75" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="9.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.5833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5833333333333" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:13">
-      <c r="J1" s="1" t="s">
+    <row r="1" customHeight="1" spans="3:17">
+      <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:13">
-      <c r="J2" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:17">
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1274,8 +1335,29 @@
       <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1297,31 +1379,71 @@
       <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1">
+        <v>90</v>
+      </c>
+      <c r="M4" s="1">
+        <v>300</v>
+      </c>
+      <c r="N4" s="1">
+        <v>540</v>
+      </c>
+      <c r="O4" s="1">
+        <v>870</v>
+      </c>
+      <c r="P4" s="1">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
+        <v>18</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1331,22 +1453,25 @@
       <c r="E6" s="2">
         <v>9</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
+        <v>50</v>
+      </c>
+      <c r="G6" s="4">
         <v>2100001</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>13</v>
+      <c r="H6" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
+        <v>21</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1356,22 +1481,25 @@
       <c r="E7" s="2">
         <v>9</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
+        <v>50</v>
+      </c>
+      <c r="G7" s="4">
         <v>2100002</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>16</v>
+      <c r="H7" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
+        <v>24</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1381,21 +1509,24 @@
       <c r="E8" s="2">
         <v>9</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
+        <v>50</v>
+      </c>
+      <c r="G8" s="4">
         <v>2100003</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>18</v>
+      <c r="H8" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>26</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1405,21 +1536,24 @@
       <c r="E9" s="2">
         <v>8</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
+        <v>50</v>
+      </c>
+      <c r="G9" s="4">
         <v>2100004</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>13</v>
+      <c r="H9" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+        <v>21</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="3:17">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1429,22 +1563,25 @@
       <c r="E10" s="2">
         <v>8</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
+        <v>50</v>
+      </c>
+      <c r="G10" s="4">
         <v>2100005</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>16</v>
+      <c r="H10" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>24</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1454,22 +1591,25 @@
       <c r="E11" s="2">
         <v>8</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
+        <v>50</v>
+      </c>
+      <c r="G11" s="4">
         <v>2100006</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>18</v>
+      <c r="H11" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>26</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -1479,22 +1619,25 @@
       <c r="E12" s="2">
         <v>7</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
+        <v>60</v>
+      </c>
+      <c r="G12" s="4">
         <v>2100007</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>24</v>
+      <c r="H12" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="3:13">
+        <v>32</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="3:17">
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -1504,21 +1647,24 @@
       <c r="E13" s="2">
         <v>7</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
+        <v>60</v>
+      </c>
+      <c r="G13" s="4">
         <v>2100008</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>27</v>
+      <c r="H13" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
+        <v>35</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:17">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1528,21 +1674,24 @@
       <c r="E14" s="2">
         <v>7</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
+        <v>60</v>
+      </c>
+      <c r="G14" s="4">
         <v>2100009</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>29</v>
+      <c r="H14" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" customHeight="1" spans="3:13">
+        <v>37</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:17">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1552,21 +1701,24 @@
       <c r="E15" s="2">
         <v>6</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
+        <v>70</v>
+      </c>
+      <c r="G15" s="4">
         <v>2100010</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>24</v>
+      <c r="H15" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="3:13">
+        <v>32</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:17">
       <c r="C16" s="2">
         <v>11</v>
       </c>
@@ -1576,21 +1728,24 @@
       <c r="E16" s="2">
         <v>6</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
+        <v>70</v>
+      </c>
+      <c r="G16" s="4">
         <v>2100011</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>27</v>
+      <c r="H16" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>35</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C17" s="2">
         <v>12</v>
       </c>
@@ -1600,22 +1755,25 @@
       <c r="E17" s="2">
         <v>6</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
+        <v>70</v>
+      </c>
+      <c r="G17" s="4">
         <v>2100012</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>29</v>
+      <c r="H17" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="1"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:13">
+        <v>37</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="C18" s="2">
         <v>13</v>
       </c>
@@ -1625,21 +1783,24 @@
       <c r="E18" s="2">
         <v>5</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" s="4">
         <v>2100013</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>35</v>
+      <c r="H18" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="M18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:13">
+        <v>43</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:14">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2">
@@ -1651,21 +1812,24 @@
       <c r="E19" s="2">
         <v>5</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" s="4">
         <v>2100014</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>38</v>
+      <c r="H19" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:13">
+        <v>46</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="C20" s="2">
         <v>15</v>
       </c>
@@ -1675,22 +1839,25 @@
       <c r="E20" s="2">
         <v>5</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" s="4">
         <v>2100015</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>40</v>
+      <c r="H20" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="2"/>
-      <c r="M20" s="1"/>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:13">
+        <v>48</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="C21" s="2">
         <v>16</v>
       </c>
@@ -1700,22 +1867,25 @@
       <c r="E21" s="2">
         <v>4</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
+        <v>90</v>
+      </c>
+      <c r="G21" s="4">
         <v>2100016</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>35</v>
+      <c r="H21" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="2"/>
-      <c r="M21" s="1"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>43</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2">
@@ -1727,22 +1897,25 @@
       <c r="E22" s="2">
         <v>4</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
+        <v>90</v>
+      </c>
+      <c r="G22" s="4">
         <v>2100017</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>38</v>
+      <c r="H22" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" s="1"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:13">
+        <v>46</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:14">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2">
@@ -1754,21 +1927,24 @@
       <c r="E23" s="2">
         <v>4</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
+        <v>90</v>
+      </c>
+      <c r="G23" s="4">
         <v>2100018</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>40</v>
+      <c r="H23" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:13">
+        <v>48</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="C24" s="2">
         <v>19</v>
       </c>
@@ -1778,23 +1954,26 @@
       <c r="E24" s="2">
         <v>3</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
+        <v>100</v>
+      </c>
+      <c r="G24" s="4">
         <v>2100019</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>46</v>
+      <c r="H24" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>55</v>
+      </c>
       <c r="K24" s="1"/>
-      <c r="M24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:13">
+      <c r="L24" s="1"/>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:14">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2">
@@ -1806,21 +1985,24 @@
       <c r="E25" s="2">
         <v>3</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
+        <v>100</v>
+      </c>
+      <c r="G25" s="4">
         <v>2100020</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>49</v>
+      <c r="H25" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:13">
+        <v>57</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:14">
       <c r="C26" s="2">
         <v>21</v>
       </c>
@@ -1830,21 +2012,24 @@
       <c r="E26" s="2">
         <v>3</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
+        <v>100</v>
+      </c>
+      <c r="G26" s="4">
         <v>2100021</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>51</v>
+      <c r="H26" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:13">
+        <v>59</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:14">
       <c r="C27" s="2">
         <v>22</v>
       </c>
@@ -1854,21 +2039,24 @@
       <c r="E27" s="2">
         <v>2</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
+        <v>150</v>
+      </c>
+      <c r="G27" s="4">
         <v>2100022</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>46</v>
+      <c r="H27" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:13">
+        <v>54</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:14">
       <c r="C28" s="2">
         <v>23</v>
       </c>
@@ -1878,21 +2066,24 @@
       <c r="E28" s="2">
         <v>2</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
+        <v>150</v>
+      </c>
+      <c r="G28" s="4">
         <v>2100023</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>49</v>
+      <c r="H28" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:13">
+        <v>57</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
       <c r="C29" s="2">
         <v>24</v>
       </c>
@@ -1902,21 +2093,24 @@
       <c r="E29" s="2">
         <v>2</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
+        <v>150</v>
+      </c>
+      <c r="G29" s="4">
         <v>2100024</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>51</v>
+      <c r="H29" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:13">
+        <v>59</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:14">
       <c r="C30" s="2">
         <v>25</v>
       </c>
@@ -1926,21 +2120,24 @@
       <c r="E30" s="2">
         <v>1</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
+        <v>200</v>
+      </c>
+      <c r="G30" s="4">
         <v>2100025</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>57</v>
+      <c r="H30" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:13">
+        <v>65</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:14">
       <c r="C31" s="2">
         <v>26</v>
       </c>
@@ -1950,21 +2147,24 @@
       <c r="E31" s="2">
         <v>1</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
+        <v>200</v>
+      </c>
+      <c r="G31" s="4">
         <v>2100026</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>57</v>
+      <c r="H31" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:13">
+        <v>65</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:14">
       <c r="C32" s="2">
         <v>27</v>
       </c>
@@ -1974,187 +2174,209 @@
       <c r="E32" s="2">
         <v>1</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
+        <v>200</v>
+      </c>
+      <c r="G32" s="4">
         <v>2100027</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>57</v>
+      <c r="H32" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:12">
+        <v>65</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:13">
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="H33" s="2"/>
+      <c r="F33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" customHeight="1" spans="3:12">
+      <c r="J33" s="2"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" customHeight="1" spans="3:13">
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="H34" s="7"/>
       <c r="I34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" customHeight="1" spans="3:12">
+      <c r="J34" s="2"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" customHeight="1" spans="3:13">
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" customHeight="1" spans="3:12">
+      <c r="F35" s="2"/>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="H36" s="2"/>
+      <c r="F36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" customHeight="1" spans="3:12">
+      <c r="J36" s="2"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" customHeight="1" spans="3:13">
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="F37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" customHeight="1" spans="3:12">
+      <c r="J37" s="2"/>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="H38" s="2"/>
+      <c r="F38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:12">
+      <c r="J38" s="2"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="H39" s="2"/>
+      <c r="F39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" customHeight="1" spans="3:12">
+      <c r="J39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="H40" s="2"/>
+      <c r="F40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="L40" s="2"/>
-    </row>
-    <row r="41" customHeight="1" spans="3:12">
+      <c r="J40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="H41" s="2"/>
+      <c r="F41" s="2"/>
       <c r="I41" s="2"/>
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" customHeight="1" spans="3:12">
+      <c r="J41" s="2"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="H42" s="2"/>
+      <c r="F42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" customHeight="1" spans="3:12">
+      <c r="J42" s="2"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="H43" s="7"/>
       <c r="I43" s="2"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" customHeight="1" spans="3:12">
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" customHeight="1" spans="3:12">
+      <c r="J43" s="2"/>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="H45" s="2"/>
+      <c r="F45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" customHeight="1" spans="3:12">
+      <c r="J45" s="2"/>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="F46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" customHeight="1" spans="3:12">
+      <c r="J46" s="2"/>
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" customHeight="1" spans="3:13">
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="H47" s="2"/>
+      <c r="F47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="L47" s="2"/>
-    </row>
-    <row r="48" customHeight="1" spans="3:12">
+      <c r="J47" s="2"/>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="H48" s="2"/>
+      <c r="F48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="L48" s="2"/>
-    </row>
-    <row r="49" customHeight="1" spans="3:12">
+      <c r="J48" s="2"/>
+      <c r="M48" s="2"/>
+    </row>
+    <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="F49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="L49" s="2"/>
-    </row>
-    <row r="50" customHeight="1" spans="3:12">
+      <c r="J49" s="2"/>
+      <c r="M49" s="2"/>
+    </row>
+    <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="H50" s="2"/>
+      <c r="F50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="L50" s="2"/>
-    </row>
-    <row r="51" customHeight="1" spans="3:12">
+      <c r="J50" s="2"/>
+      <c r="M50" s="2"/>
+    </row>
+    <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="H51" s="2"/>
+      <c r="F51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="L51" s="2"/>
-    </row>
-    <row r="52" customHeight="1" spans="3:12">
+      <c r="J51" s="2"/>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="H52" s="7"/>
       <c r="I52" s="2"/>
-      <c r="L52" s="2"/>
-    </row>
-    <row r="53" customHeight="1" spans="3:12">
-      <c r="L53" s="2"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:12">
-      <c r="L54" s="2"/>
-    </row>
-    <row r="55" customHeight="1" spans="3:12">
-      <c r="L55" s="2"/>
-    </row>
-    <row r="56" customHeight="1" spans="3:12">
-      <c r="L56" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="M52" s="2"/>
+    </row>
+    <row r="53" customHeight="1" spans="3:13">
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:13">
+      <c r="M54" s="2"/>
+    </row>
+    <row r="55" customHeight="1" spans="3:13">
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:13">
+      <c r="M56" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4 F5 C3:E5 G3:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -95,7 +95,7 @@
     <t>2001,2003,2010,2013,2004,2007,91,95</t>
   </si>
   <si>
-    <t>3,3,3,3,3,3,0.3,3</t>
+    <t>3,4.5,3,3,3,3,0.4,3</t>
   </si>
   <si>
     <t>刘备</t>
@@ -113,7 +113,7 @@
     <t>赵云</t>
   </si>
   <si>
-    <t>2.5,2.5,2.5,2.5,2.5,2.5,0.2,2</t>
+    <t>2.5,3.7,2.5,2.5,2.5,2.5,0.3,2</t>
   </si>
   <si>
     <t>张飞</t>
@@ -128,7 +128,7 @@
     <t>2001,2003,2010,2013,2007,91,95</t>
   </si>
   <si>
-    <t>2,2,2,2,2,0.1,1.5</t>
+    <t>2,3,2,2,2,0.2,1.5</t>
   </si>
   <si>
     <t>黄忠</t>
@@ -146,7 +146,7 @@
     <t>关银屏</t>
   </si>
   <si>
-    <t>1.5,1.5,1.5,1.5,1.5,0.1,1.2</t>
+    <t>1.5,2.3,1.5,1.5,1.5,0.1,1.2</t>
   </si>
   <si>
     <t>张星彩</t>
@@ -161,27 +161,10 @@
     <t>2001,2003,2010,2013,91,95</t>
   </si>
   <si>
-    <t>1.4,1.4,1.4,1.4,0.1,1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>姜维</t>
-    </r>
+    <t>1.4,2.1,1.4,1.4,0.1,1</t>
+  </si>
+  <si>
+    <t>姜维</t>
   </si>
   <si>
     <t>2001,2003,2010,2013,92,95</t>
@@ -196,7 +179,7 @@
     <t>伊籍</t>
   </si>
   <si>
-    <t>1.3,1.3,1.3,1.3,0.1,0.8</t>
+    <t>1.3,1.9,1.3,1.3,0.1,0.8</t>
   </si>
   <si>
     <t>徐庶</t>
@@ -211,7 +194,7 @@
     <t>2001,2003,2013,2007,95</t>
   </si>
   <si>
-    <t>1.2,1.2,1.2,1.2,0.5</t>
+    <t>1.2,1.8,1.2,1.2,0.5</t>
   </si>
   <si>
     <t>王平</t>
@@ -226,27 +209,10 @@
     <t>2001,2003,2013,2009,95</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>徐庶</t>
-    </r>
-  </si>
-  <si>
-    <t>1.1,1.1,1.1,1.1,0.3</t>
+    <t>马谡</t>
+  </si>
+  <si>
+    <t>1.1,1.6,1.1,1.1,0.3</t>
   </si>
   <si>
     <t>张苞</t>
@@ -261,7 +227,7 @@
     <t>2001,2003,2013,95</t>
   </si>
   <si>
-    <t>1,1,1,0.1</t>
+    <t>1,1.5,1,0.1</t>
   </si>
   <si>
     <t>周仓</t>
@@ -280,7 +246,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,12 +271,6 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -793,137 +753,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -934,7 +894,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1462,10 +1421,10 @@
       <c r="H6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="2"/>
@@ -1490,10 +1449,10 @@
       <c r="H7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="2"/>
@@ -1518,10 +1477,10 @@
       <c r="H8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="8" t="s">
         <v>22</v>
       </c>
       <c r="N8" s="1"/>
@@ -1545,10 +1504,10 @@
       <c r="H9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="8" t="s">
         <v>28</v>
       </c>
       <c r="M9" s="2"/>
@@ -1572,10 +1531,10 @@
       <c r="H10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="8" t="s">
         <v>28</v>
       </c>
       <c r="K10" s="1"/>
@@ -1600,10 +1559,10 @@
       <c r="H11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>28</v>
       </c>
       <c r="K11" s="1"/>
@@ -1628,10 +1587,10 @@
       <c r="H12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K12" s="1"/>
@@ -1656,10 +1615,10 @@
       <c r="H13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M13" s="2"/>
@@ -1683,10 +1642,10 @@
       <c r="H14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M14" s="2"/>
@@ -1710,10 +1669,10 @@
       <c r="H15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="8" t="s">
         <v>39</v>
       </c>
       <c r="M15" s="2"/>
@@ -1737,10 +1696,10 @@
       <c r="H16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="8" t="s">
         <v>39</v>
       </c>
       <c r="M16" s="2"/>
@@ -1764,10 +1723,10 @@
       <c r="H17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>39</v>
       </c>
       <c r="K17" s="1"/>
@@ -1792,10 +1751,10 @@
       <c r="H18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="8" t="s">
         <v>44</v>
       </c>
       <c r="N18" s="1"/>
@@ -1818,13 +1777,13 @@
       <c r="G19" s="4">
         <v>2100014</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="8" t="s">
         <v>44</v>
       </c>
       <c r="M19" s="2"/>
@@ -1848,10 +1807,10 @@
       <c r="H20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="8" t="s">
         <v>44</v>
       </c>
       <c r="K20" s="2"/>
@@ -1876,10 +1835,10 @@
       <c r="H21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="8" t="s">
         <v>50</v>
       </c>
       <c r="K21" s="2"/>
@@ -1906,10 +1865,10 @@
       <c r="H22" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="8" t="s">
         <v>50</v>
       </c>
       <c r="K22" s="1"/>
@@ -1936,10 +1895,10 @@
       <c r="H23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="8" t="s">
         <v>50</v>
       </c>
       <c r="M23" s="2"/>
@@ -1960,13 +1919,13 @@
       <c r="G24" s="4">
         <v>2100019</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="8" t="s">
         <v>55</v>
       </c>
       <c r="K24" s="1"/>
@@ -1994,10 +1953,10 @@
       <c r="H25" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="8" t="s">
         <v>55</v>
       </c>
       <c r="M25" s="2"/>
@@ -2021,10 +1980,10 @@
       <c r="H26" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="8" t="s">
         <v>55</v>
       </c>
       <c r="M26" s="2"/>
@@ -2045,13 +2004,13 @@
       <c r="G27" s="4">
         <v>2100022</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="8" t="s">
         <v>61</v>
       </c>
       <c r="M27" s="2"/>
@@ -2072,13 +2031,13 @@
       <c r="G28" s="4">
         <v>2100023</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="8" t="s">
         <v>61</v>
       </c>
       <c r="M28" s="2"/>
@@ -2099,13 +2058,13 @@
       <c r="G29" s="4">
         <v>2100024</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="8" t="s">
         <v>61</v>
       </c>
       <c r="M29" s="2"/>
@@ -2129,10 +2088,10 @@
       <c r="H30" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="8" t="s">
         <v>66</v>
       </c>
       <c r="M30" s="2"/>
@@ -2153,13 +2112,13 @@
       <c r="G31" s="4">
         <v>2100026</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="8" t="s">
         <v>66</v>
       </c>
       <c r="M31" s="2"/>
@@ -2183,10 +2142,10 @@
       <c r="H32" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="8" t="s">
         <v>66</v>
       </c>
       <c r="M32" s="2"/>
@@ -2203,7 +2162,7 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="H34" s="7"/>
+      <c r="H34" s="6"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="M34" s="2"/>
@@ -2281,7 +2240,7 @@
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="H43" s="7"/>
+      <c r="H43" s="6"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="M43" s="2"/>
@@ -2357,7 +2316,7 @@
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="H52" s="7"/>
+      <c r="H52" s="6"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="M52" s="2"/>
@@ -2376,7 +2335,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4 F5 C3:E5 G3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -134,13 +134,13 @@
     <t>黄忠</t>
   </si>
   <si>
-    <t>2001,2003,2010,2013,2007,92,95</t>
+    <t>2001,2003,2010,2013,2008,92,95</t>
   </si>
   <si>
     <t>黄月英</t>
   </si>
   <si>
-    <t>2001,2003,2010,2013,2007,93,95</t>
+    <t>2001,2003,2010,2013,2009,93,95</t>
   </si>
   <si>
     <t>关银屏</t>

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -59,21 +59,6 @@
     <t>19:30开始测试掉落</t>
   </si>
   <si>
-    <t xml:space="preserve">橙色 </t>
-  </si>
-  <si>
-    <t>紫色</t>
-  </si>
-  <si>
-    <t>蓝色</t>
-  </si>
-  <si>
-    <t>绿色</t>
-  </si>
-  <si>
-    <t>白色</t>
-  </si>
-  <si>
     <t>9:30结束</t>
   </si>
   <si>
@@ -95,7 +80,7 @@
     <t>2001,2003,2010,2013,2004,2007,91,95</t>
   </si>
   <si>
-    <t>3,4.5,3,3,3,3,0.4,3</t>
+    <t>4,6,4,4,4,4,0.4,3</t>
   </si>
   <si>
     <t>刘备</t>
@@ -113,7 +98,7 @@
     <t>赵云</t>
   </si>
   <si>
-    <t>2.5,3.7,2.5,2.5,2.5,2.5,0.3,2</t>
+    <t>3,5,3,3,3,3,0.3,2</t>
   </si>
   <si>
     <t>张飞</t>
@@ -128,7 +113,7 @@
     <t>2001,2003,2010,2013,2007,91,95</t>
   </si>
   <si>
-    <t>2,3,2,2,2,0.2,1.5</t>
+    <t>2,4,2,2,2,0.2,1.5</t>
   </si>
   <si>
     <t>黄忠</t>
@@ -146,7 +131,7 @@
     <t>关银屏</t>
   </si>
   <si>
-    <t>1.5,2.3,1.5,1.5,1.5,0.1,1.2</t>
+    <t>1.5,3,1.5,1.5,1.5,0.1,1.2</t>
   </si>
   <si>
     <t>张星彩</t>
@@ -161,7 +146,7 @@
     <t>2001,2003,2010,2013,91,95</t>
   </si>
   <si>
-    <t>1.4,2.1,1.4,1.4,0.1,1</t>
+    <t>1.4,2.5,1.4,1.4,0.1,1</t>
   </si>
   <si>
     <t>姜维</t>
@@ -179,7 +164,7 @@
     <t>伊籍</t>
   </si>
   <si>
-    <t>1.3,1.9,1.3,1.3,0.1,0.8</t>
+    <t>1.3,2,2.3,1.3,0.1,0.8</t>
   </si>
   <si>
     <t>徐庶</t>
@@ -1214,65 +1199,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
     <col min="7" max="7" width="9.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="34.5833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.3333333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.5833333333333" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:17">
+    <row r="1" customHeight="1" spans="3:14">
       <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:17">
+    </row>
+    <row r="2" customHeight="1" spans="3:14">
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:17">
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1300,23 +1249,8 @@
       <c r="K3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:17">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1342,67 +1276,36 @@
         <v>8</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="1">
-        <v>90</v>
-      </c>
-      <c r="M4" s="1">
-        <v>300</v>
-      </c>
-      <c r="N4" s="1">
-        <v>540</v>
-      </c>
-      <c r="O4" s="1">
-        <v>870</v>
-      </c>
-      <c r="P4" s="1">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1">
-        <v>3</v>
-      </c>
-      <c r="N5" s="1">
-        <v>3</v>
-      </c>
-      <c r="O5" s="1">
-        <v>3</v>
-      </c>
-      <c r="P5" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1419,18 +1322,18 @@
         <v>2100001</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K6" s="2"/>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:17">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1447,18 +1350,18 @@
         <v>2100002</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K7" s="2"/>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:17">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1475,17 +1378,17 @@
         <v>2100003</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1502,17 +1405,17 @@
         <v>2100004</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="3:17">
+    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1529,18 +1432,18 @@
         <v>2100005</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K10" s="1"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1557,18 +1460,18 @@
         <v>2100006</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K11" s="1"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -1585,18 +1488,18 @@
         <v>2100007</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K12" s="1"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" customHeight="1" spans="3:17">
+    <row r="13" customHeight="1" spans="3:14">
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -1613,17 +1516,17 @@
         <v>2100008</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" customHeight="1" spans="3:17">
+    <row r="14" customHeight="1" spans="3:14">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1640,17 +1543,17 @@
         <v>2100009</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" customHeight="1" spans="3:17">
+    <row r="15" customHeight="1" spans="3:14">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1667,17 +1570,17 @@
         <v>2100010</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" customHeight="1" spans="3:17">
+    <row r="16" customHeight="1" spans="3:14">
       <c r="C16" s="2">
         <v>11</v>
       </c>
@@ -1694,13 +1597,13 @@
         <v>2100011</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M16" s="2"/>
     </row>
@@ -1721,13 +1624,13 @@
         <v>2100012</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K17" s="1"/>
       <c r="M17" s="2"/>
@@ -1749,13 +1652,13 @@
         <v>2100013</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N18" s="1"/>
     </row>
@@ -1778,13 +1681,13 @@
         <v>2100014</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M19" s="2"/>
     </row>
@@ -1805,13 +1708,13 @@
         <v>2100015</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K20" s="2"/>
       <c r="N20" s="1"/>
@@ -1833,13 +1736,13 @@
         <v>2100016</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K21" s="2"/>
       <c r="N21" s="1"/>
@@ -1863,13 +1766,13 @@
         <v>2100017</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K22" s="1"/>
       <c r="M22" s="2"/>
@@ -1893,13 +1796,13 @@
         <v>2100018</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M23" s="2"/>
     </row>
@@ -1920,13 +1823,13 @@
         <v>2100019</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1951,13 +1854,13 @@
         <v>2100020</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M25" s="2"/>
     </row>
@@ -1978,13 +1881,13 @@
         <v>2100021</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M26" s="2"/>
     </row>
@@ -2005,13 +1908,13 @@
         <v>2100022</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M27" s="2"/>
     </row>
@@ -2032,13 +1935,13 @@
         <v>2100023</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M28" s="2"/>
     </row>
@@ -2059,13 +1962,13 @@
         <v>2100024</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M29" s="2"/>
     </row>
@@ -2086,13 +1989,13 @@
         <v>2100025</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="M30" s="2"/>
     </row>
@@ -2113,13 +2016,13 @@
         <v>2100026</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="M31" s="2"/>
     </row>
@@ -2140,13 +2043,13 @@
         <v>2100027</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="M32" s="2"/>
     </row>

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="90">
   <si>
     <t>#</t>
   </si>
@@ -173,7 +173,7 @@
     <t>关平</t>
   </si>
   <si>
-    <t>张兴</t>
+    <t>张苞</t>
   </si>
   <si>
     <t>2001,2003,2013,2007,95</t>
@@ -200,9 +200,6 @@
     <t>1.1,1.6,1.1,1.1,0.3</t>
   </si>
   <si>
-    <t>张苞</t>
-  </si>
-  <si>
     <t>李严</t>
   </si>
   <si>
@@ -219,6 +216,162 @@
   </si>
   <si>
     <t>马岱</t>
+  </si>
+  <si>
+    <t>孙策</t>
+  </si>
+  <si>
+    <t>孙权</t>
+  </si>
+  <si>
+    <t>周瑜</t>
+  </si>
+  <si>
+    <t>陆逊</t>
+  </si>
+  <si>
+    <t>太史慈</t>
+  </si>
+  <si>
+    <t>甘宁</t>
+  </si>
+  <si>
+    <t>大乔</t>
+  </si>
+  <si>
+    <t>小乔</t>
+  </si>
+  <si>
+    <t>孙尚香</t>
+  </si>
+  <si>
+    <t>步练师</t>
+  </si>
+  <si>
+    <t>王异</t>
+  </si>
+  <si>
+    <t>辛宪英</t>
+  </si>
+  <si>
+    <t>吕蒙</t>
+  </si>
+  <si>
+    <t>黄盖</t>
+  </si>
+  <si>
+    <t>孙坚</t>
+  </si>
+  <si>
+    <t>陆抗</t>
+  </si>
+  <si>
+    <t>朱恒</t>
+  </si>
+  <si>
+    <t>吴国太</t>
+  </si>
+  <si>
+    <t>丁奉</t>
+  </si>
+  <si>
+    <t>韩当</t>
+  </si>
+  <si>
+    <r>
+      <t>程普</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蒋钦</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>周泰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>凌统</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>徐盛</t>
+    </r>
+  </si>
+  <si>
+    <t>潘璋</t>
+  </si>
+  <si>
+    <r>
+      <t>朱然</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -231,7 +384,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,6 +420,18 @@
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF191B1F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -738,137 +903,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -879,6 +1044,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1199,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1324,10 +1494,10 @@
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="2"/>
@@ -1352,10 +1522,10 @@
       <c r="H7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="11" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="2"/>
@@ -1380,10 +1550,10 @@
       <c r="H8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="11" t="s">
         <v>17</v>
       </c>
       <c r="N8" s="1"/>
@@ -1407,10 +1577,10 @@
       <c r="H9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="11" t="s">
         <v>23</v>
       </c>
       <c r="M9" s="2"/>
@@ -1434,10 +1604,10 @@
       <c r="H10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K10" s="1"/>
@@ -1462,10 +1632,10 @@
       <c r="H11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K11" s="1"/>
@@ -1490,10 +1660,10 @@
       <c r="H12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="11" t="s">
         <v>28</v>
       </c>
       <c r="K12" s="1"/>
@@ -1518,10 +1688,10 @@
       <c r="H13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="11" t="s">
         <v>28</v>
       </c>
       <c r="M13" s="2"/>
@@ -1545,10 +1715,10 @@
       <c r="H14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="11" t="s">
         <v>28</v>
       </c>
       <c r="M14" s="2"/>
@@ -1572,10 +1742,10 @@
       <c r="H15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="11" t="s">
         <v>34</v>
       </c>
       <c r="M15" s="2"/>
@@ -1599,10 +1769,10 @@
       <c r="H16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="11" t="s">
         <v>34</v>
       </c>
       <c r="M16" s="2"/>
@@ -1626,10 +1796,10 @@
       <c r="H17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K17" s="1"/>
@@ -1654,10 +1824,10 @@
       <c r="H18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="11" t="s">
         <v>39</v>
       </c>
       <c r="N18" s="1"/>
@@ -1683,10 +1853,10 @@
       <c r="H19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M19" s="2"/>
@@ -1710,10 +1880,10 @@
       <c r="H20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="11" t="s">
         <v>39</v>
       </c>
       <c r="K20" s="2"/>
@@ -1738,10 +1908,10 @@
       <c r="H21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="11" t="s">
         <v>45</v>
       </c>
       <c r="K21" s="2"/>
@@ -1768,10 +1938,10 @@
       <c r="H22" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="11" t="s">
         <v>45</v>
       </c>
       <c r="K22" s="1"/>
@@ -1798,10 +1968,10 @@
       <c r="H23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="11" t="s">
         <v>45</v>
       </c>
       <c r="M23" s="2"/>
@@ -1825,10 +1995,10 @@
       <c r="H24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="11" t="s">
         <v>50</v>
       </c>
       <c r="K24" s="1"/>
@@ -1856,10 +2026,10 @@
       <c r="H25" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="11" t="s">
         <v>50</v>
       </c>
       <c r="M25" s="2"/>
@@ -1883,10 +2053,10 @@
       <c r="H26" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" s="11" t="s">
         <v>50</v>
       </c>
       <c r="M26" s="2"/>
@@ -1910,10 +2080,10 @@
       <c r="H27" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="J27" s="11" t="s">
         <v>56</v>
       </c>
       <c r="M27" s="2"/>
@@ -1935,12 +2105,12 @@
         <v>2100023</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="11" t="s">
         <v>56</v>
       </c>
       <c r="M28" s="2"/>
@@ -1962,12 +2132,12 @@
         <v>2100024</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I29" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="11" t="s">
         <v>56</v>
       </c>
       <c r="M29" s="2"/>
@@ -1989,13 +2159,13 @@
         <v>2100025</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="J30" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="M30" s="2"/>
     </row>
@@ -2016,13 +2186,13 @@
         <v>2100026</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I31" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J31" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="M31" s="2"/>
     </row>
@@ -2043,17 +2213,17 @@
         <v>2100027</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I32" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J32" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="J32" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" customHeight="1" spans="3:13">
+    <row r="33" customHeight="1" spans="1:13">
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2061,180 +2231,889 @@
       <c r="J33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" customHeight="1" spans="3:13">
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
+    <row r="34" customHeight="1" spans="1:13">
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2">
+        <v>9</v>
+      </c>
+      <c r="F34" s="2">
+        <v>50</v>
+      </c>
+      <c r="G34" s="4">
+        <v>2100001</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" customHeight="1" spans="3:13">
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+    <row r="35" customHeight="1" spans="1:13">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2">
+        <v>9</v>
+      </c>
+      <c r="F35" s="2">
+        <v>50</v>
+      </c>
+      <c r="G35" s="4">
+        <v>2100002</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" customHeight="1" spans="3:13">
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
+    <row r="36" customHeight="1" spans="1:13">
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>3</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>9</v>
+      </c>
+      <c r="F36" s="2">
+        <v>50</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2100003</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
+    <row r="37" customHeight="1" spans="1:13">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>4</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2">
+        <v>8</v>
+      </c>
+      <c r="F37" s="2">
+        <v>50</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2100004</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
+    <row r="38" customHeight="1" spans="1:13">
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2">
+        <v>8</v>
+      </c>
+      <c r="F38" s="2">
+        <v>50</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2100005</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
+    <row r="39" customHeight="1" spans="1:13">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="2">
+        <v>6</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2">
+        <v>8</v>
+      </c>
+      <c r="F39" s="2">
+        <v>50</v>
+      </c>
+      <c r="G39" s="4">
+        <v>2100006</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
+    <row r="40" customHeight="1" spans="1:13">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="2">
+        <v>7</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2">
+        <v>7</v>
+      </c>
+      <c r="F40" s="2">
+        <v>60</v>
+      </c>
+      <c r="G40" s="4">
+        <v>2100007</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" customHeight="1" spans="3:13">
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
+    <row r="41" customHeight="1" spans="1:13">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2">
+        <v>7</v>
+      </c>
+      <c r="F41" s="2">
+        <v>60</v>
+      </c>
+      <c r="G41" s="4">
+        <v>2100008</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
+    <row r="42" customHeight="1" spans="1:13">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2">
+        <v>7</v>
+      </c>
+      <c r="F42" s="2">
+        <v>60</v>
+      </c>
+      <c r="G42" s="4">
+        <v>2100009</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
+    <row r="43" customHeight="1" spans="1:13">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2">
+        <v>6</v>
+      </c>
+      <c r="F43" s="2">
+        <v>70</v>
+      </c>
+      <c r="G43" s="4">
+        <v>2100010</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" customHeight="1" spans="3:13">
+    <row r="44" customHeight="1" spans="1:13">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="2">
+        <v>11</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2">
+        <v>6</v>
+      </c>
+      <c r="F44" s="2">
+        <v>70</v>
+      </c>
+      <c r="G44" s="4">
+        <v>2100011</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" customHeight="1" spans="3:13">
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
+    <row r="45" customHeight="1" spans="1:13">
+      <c r="A45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="2">
+        <v>12</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2">
+        <v>6</v>
+      </c>
+      <c r="F45" s="2">
+        <v>70</v>
+      </c>
+      <c r="G45" s="4">
+        <v>2100012</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" customHeight="1" spans="3:13">
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="M46" s="2"/>
-    </row>
-    <row r="47" customHeight="1" spans="3:13">
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="M47" s="2"/>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="M48" s="2"/>
-    </row>
-    <row r="49" customHeight="1" spans="3:13">
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
+    <row r="46" customHeight="1" spans="1:13">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="2">
+        <v>13</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" s="4">
+        <v>2100013</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:13">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="2">
+        <v>14</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
+      </c>
+      <c r="F47" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" s="4">
+        <v>2100014</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:13">
+      <c r="A48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="2">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2">
+        <v>5</v>
+      </c>
+      <c r="F48" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" s="4">
+        <v>2100015</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:13">
+      <c r="A49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="2">
+        <v>16</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="2">
+        <v>90</v>
+      </c>
+      <c r="G49" s="4">
+        <v>2100016</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" customHeight="1" spans="3:13">
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
+    <row r="50" customHeight="1" spans="1:13">
+      <c r="A50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="2">
+        <v>17</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2">
+        <v>4</v>
+      </c>
+      <c r="F50" s="2">
+        <v>90</v>
+      </c>
+      <c r="G50" s="4">
+        <v>2100017</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" customHeight="1" spans="3:13">
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
+    <row r="51" customHeight="1" spans="1:13">
+      <c r="A51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="2">
+        <v>18</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2">
+        <v>4</v>
+      </c>
+      <c r="F51" s="2">
+        <v>90</v>
+      </c>
+      <c r="G51" s="4">
+        <v>2100018</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" customHeight="1" spans="3:13">
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
+    <row r="52" customHeight="1" spans="1:13">
+      <c r="A52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="2">
+        <v>19</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
+      </c>
+      <c r="F52" s="2">
+        <v>100</v>
+      </c>
+      <c r="G52" s="4">
+        <v>2100019</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" customHeight="1" spans="3:13">
+    <row r="53" customHeight="1" spans="1:13">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2">
+        <v>20</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
+      </c>
+      <c r="F53" s="2">
+        <v>100</v>
+      </c>
+      <c r="G53" s="4">
+        <v>2100020</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" customHeight="1" spans="3:13">
+    <row r="54" customHeight="1" spans="1:13">
+      <c r="A54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="2">
+        <v>21</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2">
+        <v>3</v>
+      </c>
+      <c r="F54" s="2">
+        <v>100</v>
+      </c>
+      <c r="G54" s="4">
+        <v>2100021</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" customHeight="1" spans="3:13">
+    <row r="55" customHeight="1" spans="1:13">
+      <c r="A55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="2">
+        <v>22</v>
+      </c>
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2">
+        <v>2</v>
+      </c>
+      <c r="F55" s="2">
+        <v>150</v>
+      </c>
+      <c r="G55" s="4">
+        <v>2100022</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>56</v>
+      </c>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" customHeight="1" spans="3:13">
+    <row r="56" customHeight="1" spans="1:13">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="2">
+        <v>23</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2">
+        <v>2</v>
+      </c>
+      <c r="F56" s="2">
+        <v>150</v>
+      </c>
+      <c r="G56" s="4">
+        <v>2100023</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>56</v>
+      </c>
       <c r="M56" s="2"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:13">
+      <c r="A57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="2">
+        <v>24</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
+      </c>
+      <c r="F57" s="2">
+        <v>150</v>
+      </c>
+      <c r="G57" s="4">
+        <v>2100024</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:13">
+      <c r="A58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="2">
+        <v>25</v>
+      </c>
+      <c r="D58" s="2">
+        <v>2</v>
+      </c>
+      <c r="E58" s="2">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <v>200</v>
+      </c>
+      <c r="G58" s="4">
+        <v>2100025</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:13">
+      <c r="A59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="2">
+        <v>26</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2</v>
+      </c>
+      <c r="E59" s="2">
+        <v>1</v>
+      </c>
+      <c r="F59" s="2">
+        <v>200</v>
+      </c>
+      <c r="G59" s="4">
+        <v>2100026</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:13">
+      <c r="A60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="2">
+        <v>27</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2">
+        <v>200</v>
+      </c>
+      <c r="G60" s="4">
+        <v>2100027</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="90">
   <si>
     <t>#</t>
   </si>
@@ -279,6 +279,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>程普</t>
     </r>
     <r>
@@ -293,6 +299,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>‌</t>
     </r>
     <r>
@@ -307,6 +319,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>周泰</t>
     </r>
     <r>
@@ -321,6 +339,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>‌</t>
     </r>
     <r>
@@ -344,6 +368,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>‌</t>
     </r>
     <r>
@@ -361,6 +391,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>朱然</t>
     </r>
     <r>
@@ -2223,7 +2259,7 @@
       </c>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" customHeight="1" spans="1:13">
+    <row r="33" customHeight="1" spans="3:13">
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2231,15 +2267,9 @@
       <c r="J33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" customHeight="1" spans="1:13">
-      <c r="A34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="34" customHeight="1" spans="3:13">
       <c r="C34" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D34" s="2">
         <v>2</v>
@@ -2251,7 +2281,7 @@
         <v>50</v>
       </c>
       <c r="G34" s="4">
-        <v>2100001</v>
+        <v>2100028</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>63</v>
@@ -2264,15 +2294,9 @@
       </c>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" customHeight="1" spans="1:13">
-      <c r="A35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="35" customHeight="1" spans="3:13">
       <c r="C35" s="2">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2">
         <v>2</v>
@@ -2284,7 +2308,7 @@
         <v>50</v>
       </c>
       <c r="G35" s="4">
-        <v>2100002</v>
+        <v>2100029</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>64</v>
@@ -2297,15 +2321,9 @@
       </c>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" customHeight="1" spans="1:13">
-      <c r="A36" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="36" customHeight="1" spans="3:13">
       <c r="C36" s="2">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D36" s="2">
         <v>2</v>
@@ -2317,7 +2335,7 @@
         <v>50</v>
       </c>
       <c r="G36" s="4">
-        <v>2100003</v>
+        <v>2100030</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>65</v>
@@ -2330,15 +2348,9 @@
       </c>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" customHeight="1" spans="1:13">
-      <c r="A37" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="37" customHeight="1" spans="3:13">
       <c r="C37" s="2">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D37" s="2">
         <v>2</v>
@@ -2350,7 +2362,7 @@
         <v>50</v>
       </c>
       <c r="G37" s="4">
-        <v>2100004</v>
+        <v>2100031</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>66</v>
@@ -2363,15 +2375,9 @@
       </c>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" customHeight="1" spans="1:13">
-      <c r="A38" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="38" customHeight="1" spans="3:13">
       <c r="C38" s="2">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D38" s="2">
         <v>2</v>
@@ -2383,7 +2389,7 @@
         <v>50</v>
       </c>
       <c r="G38" s="4">
-        <v>2100005</v>
+        <v>2100032</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>67</v>
@@ -2396,15 +2402,9 @@
       </c>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" customHeight="1" spans="1:13">
-      <c r="A39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="39" customHeight="1" spans="3:13">
       <c r="C39" s="2">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D39" s="2">
         <v>2</v>
@@ -2416,7 +2416,7 @@
         <v>50</v>
       </c>
       <c r="G39" s="4">
-        <v>2100006</v>
+        <v>2100033</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>68</v>
@@ -2429,15 +2429,9 @@
       </c>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" customHeight="1" spans="1:13">
-      <c r="A40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="40" customHeight="1" spans="3:13">
       <c r="C40" s="2">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D40" s="2">
         <v>2</v>
@@ -2449,7 +2443,7 @@
         <v>60</v>
       </c>
       <c r="G40" s="4">
-        <v>2100007</v>
+        <v>2100034</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>69</v>
@@ -2462,15 +2456,9 @@
       </c>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" customHeight="1" spans="1:13">
-      <c r="A41" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="41" customHeight="1" spans="3:13">
       <c r="C41" s="2">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D41" s="2">
         <v>2</v>
@@ -2482,7 +2470,7 @@
         <v>60</v>
       </c>
       <c r="G41" s="4">
-        <v>2100008</v>
+        <v>2100035</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>70</v>
@@ -2495,15 +2483,9 @@
       </c>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" customHeight="1" spans="1:13">
-      <c r="A42" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="42" customHeight="1" spans="3:13">
       <c r="C42" s="2">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D42" s="2">
         <v>2</v>
@@ -2515,7 +2497,7 @@
         <v>60</v>
       </c>
       <c r="G42" s="4">
-        <v>2100009</v>
+        <v>2100036</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>71</v>
@@ -2528,15 +2510,9 @@
       </c>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" customHeight="1" spans="1:13">
-      <c r="A43" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="43" customHeight="1" spans="3:13">
       <c r="C43" s="2">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D43" s="2">
         <v>2</v>
@@ -2548,7 +2524,7 @@
         <v>70</v>
       </c>
       <c r="G43" s="4">
-        <v>2100010</v>
+        <v>2100037</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>72</v>
@@ -2561,15 +2537,9 @@
       </c>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" customHeight="1" spans="1:13">
-      <c r="A44" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="44" customHeight="1" spans="3:13">
       <c r="C44" s="2">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D44" s="2">
         <v>2</v>
@@ -2581,7 +2551,7 @@
         <v>70</v>
       </c>
       <c r="G44" s="4">
-        <v>2100011</v>
+        <v>2100038</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>73</v>
@@ -2594,15 +2564,9 @@
       </c>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" customHeight="1" spans="1:13">
-      <c r="A45" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="45" customHeight="1" spans="3:13">
       <c r="C45" s="2">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D45" s="2">
         <v>2</v>
@@ -2614,7 +2578,7 @@
         <v>70</v>
       </c>
       <c r="G45" s="4">
-        <v>2100012</v>
+        <v>2100039</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>74</v>
@@ -2627,15 +2591,9 @@
       </c>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" customHeight="1" spans="1:13">
-      <c r="A46" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="46" customHeight="1" spans="3:13">
       <c r="C46" s="2">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D46" s="2">
         <v>2</v>
@@ -2647,7 +2605,7 @@
         <v>80</v>
       </c>
       <c r="G46" s="4">
-        <v>2100013</v>
+        <v>2100040</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>75</v>
@@ -2659,15 +2617,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:13">
-      <c r="A47" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="47" customHeight="1" spans="3:13">
       <c r="C47" s="2">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D47" s="2">
         <v>2</v>
@@ -2679,7 +2631,7 @@
         <v>80</v>
       </c>
       <c r="G47" s="4">
-        <v>2100014</v>
+        <v>2100041</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>76</v>
@@ -2691,15 +2643,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:13">
-      <c r="A48" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="2">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D48" s="2">
         <v>2</v>
@@ -2711,7 +2657,7 @@
         <v>80</v>
       </c>
       <c r="G48" s="4">
-        <v>2100015</v>
+        <v>2100042</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>77</v>
@@ -2723,15 +2669,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:13">
-      <c r="A49" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="2">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D49" s="2">
         <v>2</v>
@@ -2743,7 +2683,7 @@
         <v>90</v>
       </c>
       <c r="G49" s="4">
-        <v>2100016</v>
+        <v>2100043</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>78</v>
@@ -2756,15 +2696,9 @@
       </c>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" customHeight="1" spans="1:13">
-      <c r="A50" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="2">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D50" s="2">
         <v>2</v>
@@ -2776,7 +2710,7 @@
         <v>90</v>
       </c>
       <c r="G50" s="4">
-        <v>2100017</v>
+        <v>2100044</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>79</v>
@@ -2789,15 +2723,9 @@
       </c>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" customHeight="1" spans="1:13">
-      <c r="A51" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="2">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D51" s="2">
         <v>2</v>
@@ -2809,7 +2737,7 @@
         <v>90</v>
       </c>
       <c r="G51" s="4">
-        <v>2100018</v>
+        <v>2100045</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>80</v>
@@ -2822,15 +2750,9 @@
       </c>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" customHeight="1" spans="1:13">
-      <c r="A52" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="2">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D52" s="2">
         <v>2</v>
@@ -2842,7 +2764,7 @@
         <v>100</v>
       </c>
       <c r="G52" s="4">
-        <v>2100019</v>
+        <v>2100046</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>81</v>
@@ -2855,15 +2777,9 @@
       </c>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" customHeight="1" spans="1:13">
-      <c r="A53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="2">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D53" s="2">
         <v>2</v>
@@ -2875,7 +2791,7 @@
         <v>100</v>
       </c>
       <c r="G53" s="4">
-        <v>2100020</v>
+        <v>2100047</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>82</v>
@@ -2888,15 +2804,9 @@
       </c>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" customHeight="1" spans="1:13">
-      <c r="A54" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="54" customHeight="1" spans="3:13">
       <c r="C54" s="2">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="D54" s="2">
         <v>2</v>
@@ -2908,7 +2818,7 @@
         <v>100</v>
       </c>
       <c r="G54" s="4">
-        <v>2100021</v>
+        <v>2100048</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>83</v>
@@ -2921,15 +2831,9 @@
       </c>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" customHeight="1" spans="1:13">
-      <c r="A55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="2">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D55" s="2">
         <v>2</v>
@@ -2941,7 +2845,7 @@
         <v>150</v>
       </c>
       <c r="G55" s="4">
-        <v>2100022</v>
+        <v>2100049</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>84</v>
@@ -2954,15 +2858,9 @@
       </c>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" customHeight="1" spans="1:13">
-      <c r="A56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="2">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2">
         <v>2</v>
@@ -2974,7 +2872,7 @@
         <v>150</v>
       </c>
       <c r="G56" s="4">
-        <v>2100023</v>
+        <v>2100050</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>85</v>
@@ -2987,15 +2885,9 @@
       </c>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" customHeight="1" spans="1:13">
-      <c r="A57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="2">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="D57" s="2">
         <v>2</v>
@@ -3007,7 +2899,7 @@
         <v>150</v>
       </c>
       <c r="G57" s="4">
-        <v>2100024</v>
+        <v>2100051</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>86</v>
@@ -3019,15 +2911,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:13">
-      <c r="A58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="2">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
@@ -3039,7 +2925,7 @@
         <v>200</v>
       </c>
       <c r="G58" s="4">
-        <v>2100025</v>
+        <v>2100052</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>87</v>
@@ -3051,15 +2937,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:13">
-      <c r="A59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="2">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D59" s="2">
         <v>2</v>
@@ -3071,7 +2951,7 @@
         <v>200</v>
       </c>
       <c r="G59" s="4">
-        <v>2100026</v>
+        <v>2100053</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>88</v>
@@ -3083,15 +2963,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:13">
-      <c r="A60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="60" customHeight="1" spans="3:13">
       <c r="C60" s="2">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D60" s="2">
         <v>2</v>
@@ -3103,7 +2977,7 @@
         <v>200</v>
       </c>
       <c r="G60" s="4">
-        <v>2100027</v>
+        <v>2100054</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>89</v>

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="117">
   <si>
     <t>#</t>
   </si>
@@ -408,6 +408,138 @@
       </rPr>
       <t>‌</t>
     </r>
+  </si>
+  <si>
+    <t>司马懿</t>
+  </si>
+  <si>
+    <t>曹操</t>
+  </si>
+  <si>
+    <t>郭嘉</t>
+  </si>
+  <si>
+    <t>张辽</t>
+  </si>
+  <si>
+    <t>许诸</t>
+  </si>
+  <si>
+    <t>荀彧</t>
+  </si>
+  <si>
+    <t>甄姬</t>
+  </si>
+  <si>
+    <t>张春华</t>
+  </si>
+  <si>
+    <t>蔡文姬</t>
+  </si>
+  <si>
+    <t>王元姬</t>
+  </si>
+  <si>
+    <t>曹华</t>
+  </si>
+  <si>
+    <t>郭皇后</t>
+  </si>
+  <si>
+    <t>于禁</t>
+  </si>
+  <si>
+    <t>李典</t>
+  </si>
+  <si>
+    <t>夏侯惇</t>
+  </si>
+  <si>
+    <t>典韦</t>
+  </si>
+  <si>
+    <t>乐进</t>
+  </si>
+  <si>
+    <t>张郃</t>
+  </si>
+  <si>
+    <t>徐晃</t>
+  </si>
+  <si>
+    <t>夏侯渊</t>
+  </si>
+  <si>
+    <t>曹洪</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>曹仁</t>
+    </r>
+  </si>
+  <si>
+    <t>曹彰</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>荀攸</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>满宠</t>
+    </r>
+  </si>
+  <si>
+    <t>陈泰</t>
+  </si>
+  <si>
+    <t>郝昭</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1201,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1085,6 +1217,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1405,7 +1540,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1530,10 +1665,10 @@
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="2"/>
@@ -1558,10 +1693,10 @@
       <c r="H7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="12" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="2"/>
@@ -1586,10 +1721,10 @@
       <c r="H8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="12" t="s">
         <v>17</v>
       </c>
       <c r="N8" s="1"/>
@@ -1613,10 +1748,10 @@
       <c r="H9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="12" t="s">
         <v>23</v>
       </c>
       <c r="M9" s="2"/>
@@ -1640,10 +1775,10 @@
       <c r="H10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K10" s="1"/>
@@ -1668,10 +1803,10 @@
       <c r="H11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K11" s="1"/>
@@ -1696,10 +1831,10 @@
       <c r="H12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K12" s="1"/>
@@ -1724,10 +1859,10 @@
       <c r="H13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="12" t="s">
         <v>28</v>
       </c>
       <c r="M13" s="2"/>
@@ -1751,10 +1886,10 @@
       <c r="H14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>28</v>
       </c>
       <c r="M14" s="2"/>
@@ -1778,10 +1913,10 @@
       <c r="H15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>34</v>
       </c>
       <c r="M15" s="2"/>
@@ -1805,10 +1940,10 @@
       <c r="H16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>34</v>
       </c>
       <c r="M16" s="2"/>
@@ -1832,10 +1967,10 @@
       <c r="H17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="12" t="s">
         <v>34</v>
       </c>
       <c r="K17" s="1"/>
@@ -1860,10 +1995,10 @@
       <c r="H18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="12" t="s">
         <v>39</v>
       </c>
       <c r="N18" s="1"/>
@@ -1889,10 +2024,10 @@
       <c r="H19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="12" t="s">
         <v>39</v>
       </c>
       <c r="M19" s="2"/>
@@ -1916,10 +2051,10 @@
       <c r="H20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="12" t="s">
         <v>39</v>
       </c>
       <c r="K20" s="2"/>
@@ -1944,10 +2079,10 @@
       <c r="H21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="12" t="s">
         <v>45</v>
       </c>
       <c r="K21" s="2"/>
@@ -1974,10 +2109,10 @@
       <c r="H22" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="12" t="s">
         <v>45</v>
       </c>
       <c r="K22" s="1"/>
@@ -2004,10 +2139,10 @@
       <c r="H23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="12" t="s">
         <v>45</v>
       </c>
       <c r="M23" s="2"/>
@@ -2031,10 +2166,10 @@
       <c r="H24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="12" t="s">
         <v>50</v>
       </c>
       <c r="K24" s="1"/>
@@ -2062,10 +2197,10 @@
       <c r="H25" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="12" t="s">
         <v>50</v>
       </c>
       <c r="M25" s="2"/>
@@ -2089,10 +2224,10 @@
       <c r="H26" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="12" t="s">
         <v>50</v>
       </c>
       <c r="M26" s="2"/>
@@ -2116,10 +2251,10 @@
       <c r="H27" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="12" t="s">
         <v>56</v>
       </c>
       <c r="M27" s="2"/>
@@ -2143,10 +2278,10 @@
       <c r="H28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="12" t="s">
         <v>56</v>
       </c>
       <c r="M28" s="2"/>
@@ -2170,10 +2305,10 @@
       <c r="H29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J29" s="12" t="s">
         <v>56</v>
       </c>
       <c r="M29" s="2"/>
@@ -2197,10 +2332,10 @@
       <c r="H30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="12" t="s">
         <v>60</v>
       </c>
       <c r="M30" s="2"/>
@@ -2224,10 +2359,10 @@
       <c r="H31" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="J31" s="12" t="s">
         <v>60</v>
       </c>
       <c r="M31" s="2"/>
@@ -2251,10 +2386,10 @@
       <c r="H32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="J32" s="11" t="s">
+      <c r="J32" s="12" t="s">
         <v>60</v>
       </c>
       <c r="M32" s="2"/>
@@ -2286,10 +2421,10 @@
       <c r="H34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="J34" s="12" t="s">
         <v>17</v>
       </c>
       <c r="M34" s="2"/>
@@ -2313,10 +2448,10 @@
       <c r="H35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J35" s="11" t="s">
+      <c r="J35" s="12" t="s">
         <v>17</v>
       </c>
       <c r="M35" s="2"/>
@@ -2340,10 +2475,10 @@
       <c r="H36" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="J36" s="12" t="s">
         <v>17</v>
       </c>
       <c r="M36" s="2"/>
@@ -2367,10 +2502,10 @@
       <c r="H37" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="11" t="s">
+      <c r="J37" s="12" t="s">
         <v>23</v>
       </c>
       <c r="M37" s="2"/>
@@ -2394,10 +2529,10 @@
       <c r="H38" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="12" t="s">
         <v>23</v>
       </c>
       <c r="M38" s="2"/>
@@ -2421,10 +2556,10 @@
       <c r="H39" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J39" s="11" t="s">
+      <c r="J39" s="12" t="s">
         <v>23</v>
       </c>
       <c r="M39" s="2"/>
@@ -2448,10 +2583,10 @@
       <c r="H40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="J40" s="12" t="s">
         <v>28</v>
       </c>
       <c r="M40" s="2"/>
@@ -2475,10 +2610,10 @@
       <c r="H41" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J41" s="11" t="s">
+      <c r="J41" s="12" t="s">
         <v>28</v>
       </c>
       <c r="M41" s="2"/>
@@ -2502,10 +2637,10 @@
       <c r="H42" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="J42" s="12" t="s">
         <v>28</v>
       </c>
       <c r="M42" s="2"/>
@@ -2529,10 +2664,10 @@
       <c r="H43" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="J43" s="12" t="s">
         <v>34</v>
       </c>
       <c r="M43" s="2"/>
@@ -2556,10 +2691,10 @@
       <c r="H44" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="J44" s="12" t="s">
         <v>34</v>
       </c>
       <c r="M44" s="2"/>
@@ -2583,10 +2718,10 @@
       <c r="H45" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="J45" s="12" t="s">
         <v>34</v>
       </c>
       <c r="M45" s="2"/>
@@ -2610,10 +2745,10 @@
       <c r="H46" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2636,10 +2771,10 @@
       <c r="H47" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="J47" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2662,10 +2797,10 @@
       <c r="H48" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2688,10 +2823,10 @@
       <c r="H49" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="12" t="s">
         <v>45</v>
       </c>
       <c r="M49" s="2"/>
@@ -2715,10 +2850,10 @@
       <c r="H50" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="12" t="s">
         <v>45</v>
       </c>
       <c r="M50" s="2"/>
@@ -2742,10 +2877,10 @@
       <c r="H51" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="12" t="s">
         <v>45</v>
       </c>
       <c r="M51" s="2"/>
@@ -2769,10 +2904,10 @@
       <c r="H52" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="12" t="s">
         <v>50</v>
       </c>
       <c r="M52" s="2"/>
@@ -2796,10 +2931,10 @@
       <c r="H53" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J53" s="12" t="s">
         <v>50</v>
       </c>
       <c r="M53" s="2"/>
@@ -2823,10 +2958,10 @@
       <c r="H54" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="12" t="s">
         <v>50</v>
       </c>
       <c r="M54" s="2"/>
@@ -2850,10 +2985,10 @@
       <c r="H55" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="12" t="s">
         <v>56</v>
       </c>
       <c r="M55" s="2"/>
@@ -2877,10 +3012,10 @@
       <c r="H56" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="12" t="s">
         <v>56</v>
       </c>
       <c r="M56" s="2"/>
@@ -2904,10 +3039,10 @@
       <c r="H57" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="J57" s="12" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2930,10 +3065,10 @@
       <c r="H58" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="12" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2956,10 +3091,10 @@
       <c r="H59" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="12" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2982,10 +3117,712 @@
       <c r="H60" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:13">
+      <c r="C62" s="2">
+        <v>55</v>
+      </c>
+      <c r="D62" s="2">
+        <v>3</v>
+      </c>
+      <c r="E62" s="2">
+        <v>9</v>
+      </c>
+      <c r="F62" s="2">
+        <v>50</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2100055</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:13">
+      <c r="C63" s="2">
+        <v>56</v>
+      </c>
+      <c r="D63" s="2">
+        <v>3</v>
+      </c>
+      <c r="E63" s="2">
+        <v>9</v>
+      </c>
+      <c r="F63" s="2">
+        <v>50</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2100056</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:13">
+      <c r="C64" s="2">
+        <v>57</v>
+      </c>
+      <c r="D64" s="2">
+        <v>3</v>
+      </c>
+      <c r="E64" s="2">
+        <v>9</v>
+      </c>
+      <c r="F64" s="2">
+        <v>50</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2100057</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="2">
+        <v>58</v>
+      </c>
+      <c r="D65" s="2">
+        <v>3</v>
+      </c>
+      <c r="E65" s="2">
+        <v>8</v>
+      </c>
+      <c r="F65" s="2">
+        <v>50</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2100058</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="2">
+        <v>59</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3</v>
+      </c>
+      <c r="E66" s="2">
+        <v>8</v>
+      </c>
+      <c r="F66" s="2">
+        <v>50</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2100059</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="2">
+        <v>60</v>
+      </c>
+      <c r="D67" s="2">
+        <v>3</v>
+      </c>
+      <c r="E67" s="2">
+        <v>8</v>
+      </c>
+      <c r="F67" s="2">
+        <v>50</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2100060</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
+      <c r="C68" s="2">
+        <v>61</v>
+      </c>
+      <c r="D68" s="2">
+        <v>3</v>
+      </c>
+      <c r="E68" s="2">
+        <v>7</v>
+      </c>
+      <c r="F68" s="2">
+        <v>60</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2100061</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="2">
+        <v>62</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3</v>
+      </c>
+      <c r="E69" s="2">
+        <v>7</v>
+      </c>
+      <c r="F69" s="2">
+        <v>60</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2100062</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
+      <c r="C70" s="2">
+        <v>63</v>
+      </c>
+      <c r="D70" s="2">
+        <v>3</v>
+      </c>
+      <c r="E70" s="2">
+        <v>7</v>
+      </c>
+      <c r="F70" s="2">
+        <v>60</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2100063</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="2">
+        <v>64</v>
+      </c>
+      <c r="D71" s="2">
+        <v>3</v>
+      </c>
+      <c r="E71" s="2">
+        <v>6</v>
+      </c>
+      <c r="F71" s="2">
+        <v>70</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2100064</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="2">
+        <v>65</v>
+      </c>
+      <c r="D72" s="2">
+        <v>3</v>
+      </c>
+      <c r="E72" s="2">
+        <v>6</v>
+      </c>
+      <c r="F72" s="2">
+        <v>70</v>
+      </c>
+      <c r="G72" s="1">
+        <v>2100065</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I72" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J72" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="2">
+        <v>66</v>
+      </c>
+      <c r="D73" s="2">
+        <v>3</v>
+      </c>
+      <c r="E73" s="2">
+        <v>6</v>
+      </c>
+      <c r="F73" s="2">
+        <v>70</v>
+      </c>
+      <c r="G73" s="1">
+        <v>2100066</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="2">
+        <v>67</v>
+      </c>
+      <c r="D74" s="2">
+        <v>3</v>
+      </c>
+      <c r="E74" s="2">
+        <v>5</v>
+      </c>
+      <c r="F74" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2100067</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="2">
+        <v>68</v>
+      </c>
+      <c r="D75" s="2">
+        <v>3</v>
+      </c>
+      <c r="E75" s="2">
+        <v>5</v>
+      </c>
+      <c r="F75" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" s="1">
+        <v>2100068</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="2">
+        <v>69</v>
+      </c>
+      <c r="D76" s="2">
+        <v>3</v>
+      </c>
+      <c r="E76" s="2">
+        <v>5</v>
+      </c>
+      <c r="F76" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2100069</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J76" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="C77" s="2">
+        <v>70</v>
+      </c>
+      <c r="D77" s="2">
+        <v>3</v>
+      </c>
+      <c r="E77" s="2">
+        <v>4</v>
+      </c>
+      <c r="F77" s="2">
+        <v>90</v>
+      </c>
+      <c r="G77" s="1">
+        <v>2100070</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="2">
+        <v>71</v>
+      </c>
+      <c r="D78" s="2">
+        <v>3</v>
+      </c>
+      <c r="E78" s="2">
+        <v>4</v>
+      </c>
+      <c r="F78" s="2">
+        <v>90</v>
+      </c>
+      <c r="G78" s="1">
+        <v>2100071</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="C79" s="2">
+        <v>72</v>
+      </c>
+      <c r="D79" s="2">
+        <v>3</v>
+      </c>
+      <c r="E79" s="2">
+        <v>4</v>
+      </c>
+      <c r="F79" s="2">
+        <v>90</v>
+      </c>
+      <c r="G79" s="1">
+        <v>2100072</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="C80" s="2">
+        <v>73</v>
+      </c>
+      <c r="D80" s="2">
+        <v>3</v>
+      </c>
+      <c r="E80" s="2">
+        <v>3</v>
+      </c>
+      <c r="F80" s="2">
+        <v>100</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2100073</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
+      <c r="C81" s="2">
+        <v>74</v>
+      </c>
+      <c r="D81" s="2">
+        <v>3</v>
+      </c>
+      <c r="E81" s="2">
+        <v>3</v>
+      </c>
+      <c r="F81" s="2">
+        <v>100</v>
+      </c>
+      <c r="G81" s="1">
+        <v>2100074</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
+      <c r="C82" s="2">
+        <v>75</v>
+      </c>
+      <c r="D82" s="2">
+        <v>3</v>
+      </c>
+      <c r="E82" s="2">
+        <v>3</v>
+      </c>
+      <c r="F82" s="2">
+        <v>100</v>
+      </c>
+      <c r="G82" s="1">
+        <v>2100075</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
+      <c r="C83" s="2">
+        <v>76</v>
+      </c>
+      <c r="D83" s="2">
+        <v>3</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2">
+        <v>150</v>
+      </c>
+      <c r="G83" s="1">
+        <v>2100076</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
+      <c r="C84" s="2">
+        <v>77</v>
+      </c>
+      <c r="D84" s="2">
+        <v>3</v>
+      </c>
+      <c r="E84" s="2">
+        <v>2</v>
+      </c>
+      <c r="F84" s="2">
+        <v>150</v>
+      </c>
+      <c r="G84" s="1">
+        <v>2100077</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J84" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
+      <c r="C85" s="2">
+        <v>78</v>
+      </c>
+      <c r="D85" s="2">
+        <v>3</v>
+      </c>
+      <c r="E85" s="2">
+        <v>2</v>
+      </c>
+      <c r="F85" s="2">
+        <v>150</v>
+      </c>
+      <c r="G85" s="1">
+        <v>2100078</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:10">
+      <c r="C86" s="2">
+        <v>79</v>
+      </c>
+      <c r="D86" s="2">
+        <v>3</v>
+      </c>
+      <c r="E86" s="2">
+        <v>1</v>
+      </c>
+      <c r="F86" s="2">
+        <v>200</v>
+      </c>
+      <c r="G86" s="1">
+        <v>2100079</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:10">
+      <c r="C87" s="2">
+        <v>80</v>
+      </c>
+      <c r="D87" s="2">
+        <v>3</v>
+      </c>
+      <c r="E87" s="2">
+        <v>1</v>
+      </c>
+      <c r="F87" s="2">
+        <v>200</v>
+      </c>
+      <c r="G87" s="1">
+        <v>2100080</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I87" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:10">
+      <c r="C88" s="2">
+        <v>81</v>
+      </c>
+      <c r="D88" s="2">
+        <v>3</v>
+      </c>
+      <c r="E88" s="2">
+        <v>1</v>
+      </c>
+      <c r="F88" s="2">
+        <v>200</v>
+      </c>
+      <c r="G88" s="1">
+        <v>2100081</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="I88" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J88" s="12" t="s">
         <v>60</v>
       </c>
     </row>

--- a/Excel/SpiritConfig.xlsx
+++ b/Excel/SpiritConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="144">
   <si>
     <t>#</t>
   </si>
@@ -541,6 +546,109 @@
   <si>
     <t>郝昭</t>
   </si>
+  <si>
+    <t>张角</t>
+  </si>
+  <si>
+    <t>左慈</t>
+  </si>
+  <si>
+    <t>吕布</t>
+  </si>
+  <si>
+    <t>于吉</t>
+  </si>
+  <si>
+    <t>袁绍</t>
+  </si>
+  <si>
+    <t>貂蝉</t>
+  </si>
+  <si>
+    <t>陈宫</t>
+  </si>
+  <si>
+    <t>华雄</t>
+  </si>
+  <si>
+    <t>董卓</t>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>袁术</t>
+    </r>
+  </si>
+  <si>
+    <t>马腾</t>
+  </si>
+  <si>
+    <t>韩遂</t>
+  </si>
+  <si>
+    <t>张宝</t>
+  </si>
+  <si>
+    <t>张梁</t>
+  </si>
+  <si>
+    <t>高顺</t>
+  </si>
+  <si>
+    <t>贾诩</t>
+  </si>
+  <si>
+    <t>华佗</t>
+  </si>
+  <si>
+    <t>颜良</t>
+  </si>
+  <si>
+    <t>文丑</t>
+  </si>
+  <si>
+    <t>沮授</t>
+  </si>
+  <si>
+    <t>田丰</t>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>纪灵</t>
+    </r>
+  </si>
+  <si>
+    <t>波才</t>
+  </si>
+  <si>
+    <t>张曼成</t>
+  </si>
+  <si>
+    <t>程远志</t>
+  </si>
+  <si>
+    <t>马元义</t>
+  </si>
+  <si>
+    <t>管亥</t>
+  </si>
 </sst>
 </file>
 
@@ -552,7 +660,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,6 +708,23 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1071,137 +1196,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1220,6 +1345,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1540,7 +1668,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1665,10 +1793,10 @@
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="15" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="2"/>
@@ -1693,10 +1821,10 @@
       <c r="H7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="15" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="2"/>
@@ -1721,10 +1849,10 @@
       <c r="H8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="15" t="s">
         <v>17</v>
       </c>
       <c r="N8" s="1"/>
@@ -1748,10 +1876,10 @@
       <c r="H9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M9" s="2"/>
@@ -1775,10 +1903,10 @@
       <c r="H10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="15" t="s">
         <v>23</v>
       </c>
       <c r="K10" s="1"/>
@@ -1803,10 +1931,10 @@
       <c r="H11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="15" t="s">
         <v>23</v>
       </c>
       <c r="K11" s="1"/>
@@ -1831,10 +1959,10 @@
       <c r="H12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="15" t="s">
         <v>28</v>
       </c>
       <c r="K12" s="1"/>
@@ -1859,10 +1987,10 @@
       <c r="H13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="15" t="s">
         <v>28</v>
       </c>
       <c r="M13" s="2"/>
@@ -1886,10 +2014,10 @@
       <c r="H14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="15" t="s">
         <v>28</v>
       </c>
       <c r="M14" s="2"/>
@@ -1913,10 +2041,10 @@
       <c r="H15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="15" t="s">
         <v>34</v>
       </c>
       <c r="M15" s="2"/>
@@ -1940,10 +2068,10 @@
       <c r="H16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="15" t="s">
         <v>34</v>
       </c>
       <c r="M16" s="2"/>
@@ -1967,10 +2095,10 @@
       <c r="H17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="15" t="s">
         <v>34</v>
       </c>
       <c r="K17" s="1"/>
@@ -1995,10 +2123,10 @@
       <c r="H18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="15" t="s">
         <v>39</v>
       </c>
       <c r="N18" s="1"/>
@@ -2024,10 +2152,10 @@
       <c r="H19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="15" t="s">
         <v>39</v>
       </c>
       <c r="M19" s="2"/>
@@ -2051,10 +2179,10 @@
       <c r="H20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="15" t="s">
         <v>39</v>
       </c>
       <c r="K20" s="2"/>
@@ -2079,10 +2207,10 @@
       <c r="H21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="15" t="s">
         <v>45</v>
       </c>
       <c r="K21" s="2"/>
@@ -2109,10 +2237,10 @@
       <c r="H22" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="15" t="s">
         <v>45</v>
       </c>
       <c r="K22" s="1"/>
@@ -2139,10 +2267,10 @@
       <c r="H23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="15" t="s">
         <v>45</v>
       </c>
       <c r="M23" s="2"/>
@@ -2166,10 +2294,10 @@
       <c r="H24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="15" t="s">
         <v>50</v>
       </c>
       <c r="K24" s="1"/>
@@ -2197,10 +2325,10 @@
       <c r="H25" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="15" t="s">
         <v>50</v>
       </c>
       <c r="M25" s="2"/>
@@ -2224,10 +2352,10 @@
       <c r="H26" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="15" t="s">
         <v>50</v>
       </c>
       <c r="M26" s="2"/>
@@ -2251,10 +2379,10 @@
       <c r="H27" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="J27" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M27" s="2"/>
@@ -2278,10 +2406,10 @@
       <c r="H28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M28" s="2"/>
@@ -2305,10 +2433,10 @@
       <c r="H29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="I29" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M29" s="2"/>
@@ -2332,10 +2460,10 @@
       <c r="H30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="15" t="s">
         <v>60</v>
       </c>
       <c r="M30" s="2"/>
@@ -2359,10 +2487,10 @@
       <c r="H31" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="15" t="s">
         <v>60</v>
       </c>
       <c r="M31" s="2"/>
@@ -2386,10 +2514,10 @@
       <c r="H32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="15" t="s">
         <v>60</v>
       </c>
       <c r="M32" s="2"/>
@@ -2421,10 +2549,10 @@
       <c r="H34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="I34" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J34" s="12" t="s">
+      <c r="J34" s="15" t="s">
         <v>17</v>
       </c>
       <c r="M34" s="2"/>
@@ -2448,10 +2576,10 @@
       <c r="H35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="J35" s="15" t="s">
         <v>17</v>
       </c>
       <c r="M35" s="2"/>
@@ -2475,10 +2603,10 @@
       <c r="H36" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="15" t="s">
         <v>17</v>
       </c>
       <c r="M36" s="2"/>
@@ -2502,10 +2630,10 @@
       <c r="H37" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="12" t="s">
+      <c r="J37" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M37" s="2"/>
@@ -2529,10 +2657,10 @@
       <c r="H38" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="I38" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="J38" s="12" t="s">
+      <c r="J38" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M38" s="2"/>
@@ -2556,10 +2684,10 @@
       <c r="H39" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="I39" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J39" s="12" t="s">
+      <c r="J39" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M39" s="2"/>
@@ -2583,10 +2711,10 @@
       <c r="H40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="I40" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J40" s="12" t="s">
+      <c r="J40" s="15" t="s">
         <v>28</v>
       </c>
       <c r="M40" s="2"/>
@@ -2610,10 +2738,10 @@
       <c r="H41" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="I41" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J41" s="12" t="s">
+      <c r="J41" s="15" t="s">
         <v>28</v>
       </c>
       <c r="M41" s="2"/>
@@ -2637,10 +2765,10 @@
       <c r="H42" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="I42" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J42" s="12" t="s">
+      <c r="J42" s="15" t="s">
         <v>28</v>
       </c>
       <c r="M42" s="2"/>
@@ -2664,10 +2792,10 @@
       <c r="H43" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I43" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="J43" s="15" t="s">
         <v>34</v>
       </c>
       <c r="M43" s="2"/>
@@ -2691,10 +2819,10 @@
       <c r="H44" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="I44" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J44" s="12" t="s">
+      <c r="J44" s="15" t="s">
         <v>34</v>
       </c>
       <c r="M44" s="2"/>
@@ -2718,10 +2846,10 @@
       <c r="H45" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="12" t="s">
+      <c r="I45" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J45" s="12" t="s">
+      <c r="J45" s="15" t="s">
         <v>34</v>
       </c>
       <c r="M45" s="2"/>
@@ -2745,10 +2873,10 @@
       <c r="H46" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="I46" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2771,10 +2899,10 @@
       <c r="H47" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="12" t="s">
+      <c r="I47" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J47" s="12" t="s">
+      <c r="J47" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2797,10 +2925,10 @@
       <c r="H48" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I48" s="12" t="s">
+      <c r="I48" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J48" s="12" t="s">
+      <c r="J48" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2823,10 +2951,10 @@
       <c r="H49" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I49" s="12" t="s">
+      <c r="I49" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="12" t="s">
+      <c r="J49" s="15" t="s">
         <v>45</v>
       </c>
       <c r="M49" s="2"/>
@@ -2850,10 +2978,10 @@
       <c r="H50" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="I50" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="15" t="s">
         <v>45</v>
       </c>
       <c r="M50" s="2"/>
@@ -2877,10 +3005,10 @@
       <c r="H51" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I51" s="12" t="s">
+      <c r="I51" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="15" t="s">
         <v>45</v>
       </c>
       <c r="M51" s="2"/>
@@ -2904,10 +3032,10 @@
       <c r="H52" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="I52" s="12" t="s">
+      <c r="I52" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="J52" s="15" t="s">
         <v>50</v>
       </c>
       <c r="M52" s="2"/>
@@ -2931,10 +3059,10 @@
       <c r="H53" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="I53" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="J53" s="15" t="s">
         <v>50</v>
       </c>
       <c r="M53" s="2"/>
@@ -2958,10 +3086,10 @@
       <c r="H54" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I54" s="12" t="s">
+      <c r="I54" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J54" s="12" t="s">
+      <c r="J54" s="15" t="s">
         <v>50</v>
       </c>
       <c r="M54" s="2"/>
@@ -2985,10 +3113,10 @@
       <c r="H55" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I55" s="12" t="s">
+      <c r="I55" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="J55" s="12" t="s">
+      <c r="J55" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M55" s="2"/>
@@ -3012,10 +3140,10 @@
       <c r="H56" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="I56" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M56" s="2"/>
@@ -3039,10 +3167,10 @@
       <c r="H57" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="I57" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="J57" s="15" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3065,10 +3193,10 @@
       <c r="H58" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3091,10 +3219,10 @@
       <c r="H59" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="I59" s="12" t="s">
+      <c r="I59" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J59" s="12" t="s">
+      <c r="J59" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3117,10 +3245,10 @@
       <c r="H60" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I60" s="12" t="s">
+      <c r="I60" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J60" s="12" t="s">
+      <c r="J60" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3143,10 +3271,10 @@
       <c r="H62" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="I62" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J62" s="12" t="s">
+      <c r="J62" s="15" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3169,10 +3297,10 @@
       <c r="H63" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I63" s="12" t="s">
+      <c r="I63" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="J63" s="12" t="s">
+      <c r="J63" s="15" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3195,10 +3323,10 @@
       <c r="H64" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I64" s="12" t="s">
+      <c r="I64" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J64" s="12" t="s">
+      <c r="J64" s="15" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3221,10 +3349,10 @@
       <c r="H65" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I65" s="12" t="s">
+      <c r="I65" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J65" s="12" t="s">
+      <c r="J65" s="15" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3247,10 +3375,10 @@
       <c r="H66" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I66" s="12" t="s">
+      <c r="I66" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="J66" s="12" t="s">
+      <c r="J66" s="15" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3273,10 +3401,10 @@
       <c r="H67" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="I67" s="12" t="s">
+      <c r="I67" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J67" s="12" t="s">
+      <c r="J67" s="15" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3299,10 +3427,10 @@
       <c r="H68" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I68" s="12" t="s">
+      <c r="I68" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J68" s="12" t="s">
+      <c r="J68" s="15" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3325,10 +3453,10 @@
       <c r="H69" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="I69" s="12" t="s">
+      <c r="I69" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J69" s="12" t="s">
+      <c r="J69" s="15" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3351,10 +3479,10 @@
       <c r="H70" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="I70" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J70" s="12" t="s">
+      <c r="J70" s="15" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3377,10 +3505,10 @@
       <c r="H71" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="I71" s="12" t="s">
+      <c r="I71" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J71" s="12" t="s">
+      <c r="J71" s="15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3403,10 +3531,10 @@
       <c r="H72" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I72" s="12" t="s">
+      <c r="I72" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J72" s="12" t="s">
+      <c r="J72" s="15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3429,10 +3557,10 @@
       <c r="H73" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="I73" s="12" t="s">
+      <c r="I73" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J73" s="12" t="s">
+      <c r="J73" s="15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3455,10 +3583,10 @@
       <c r="H74" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I74" s="12" t="s">
+      <c r="I74" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J74" s="12" t="s">
+      <c r="J74" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3481,10 +3609,10 @@
       <c r="H75" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I75" s="12" t="s">
+      <c r="I75" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J75" s="12" t="s">
+      <c r="J75" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3507,10 +3635,10 @@
       <c r="H76" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I76" s="12" t="s">
+      <c r="I76" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J76" s="12" t="s">
+      <c r="J76" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3533,10 +3661,10 @@
       <c r="H77" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I77" s="12" t="s">
+      <c r="I77" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J77" s="12" t="s">
+      <c r="J77" s="15" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3559,10 +3687,10 @@
       <c r="H78" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I78" s="12" t="s">
+      <c r="I78" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J78" s="12" t="s">
+      <c r="J78" s="15" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3585,10 +3713,10 @@
       <c r="H79" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="I79" s="12" t="s">
+      <c r="I79" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J79" s="12" t="s">
+      <c r="J79" s="15" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3611,10 +3739,10 @@
       <c r="H80" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="I80" s="12" t="s">
+      <c r="I80" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="J80" s="12" t="s">
+      <c r="J80" s="15" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3637,10 +3765,10 @@
       <c r="H81" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="I81" s="12" t="s">
+      <c r="I81" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J81" s="12" t="s">
+      <c r="J81" s="15" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3663,10 +3791,10 @@
       <c r="H82" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="I82" s="12" t="s">
+      <c r="I82" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J82" s="12" t="s">
+      <c r="J82" s="15" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3689,10 +3817,10 @@
       <c r="H83" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I83" s="12" t="s">
+      <c r="I83" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="J83" s="12" t="s">
+      <c r="J83" s="15" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3715,10 +3843,10 @@
       <c r="H84" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="I84" s="12" t="s">
+      <c r="I84" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J84" s="12" t="s">
+      <c r="J84" s="15" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3741,10 +3869,10 @@
       <c r="H85" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="I85" s="12" t="s">
+      <c r="I85" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J85" s="12" t="s">
+      <c r="J85" s="15" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3767,10 +3895,10 @@
       <c r="H86" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="I86" s="12" t="s">
+      <c r="I86" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J86" s="12" t="s">
+      <c r="J86" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3793,10 +3921,10 @@
       <c r="H87" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="I87" s="12" t="s">
+      <c r="I87" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J87" s="12" t="s">
+      <c r="J87" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3819,10 +3947,712 @@
       <c r="H88" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="I88" s="12" t="s">
+      <c r="I88" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J88" s="12" t="s">
+      <c r="J88" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:10">
+      <c r="C90" s="2">
+        <v>82</v>
+      </c>
+      <c r="D90" s="2">
+        <v>4</v>
+      </c>
+      <c r="E90" s="2">
+        <v>9</v>
+      </c>
+      <c r="F90" s="2">
+        <v>50</v>
+      </c>
+      <c r="G90" s="1">
+        <v>2100082</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I90" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:10">
+      <c r="C91" s="2">
+        <v>83</v>
+      </c>
+      <c r="D91" s="2">
+        <v>4</v>
+      </c>
+      <c r="E91" s="2">
+        <v>9</v>
+      </c>
+      <c r="F91" s="2">
+        <v>50</v>
+      </c>
+      <c r="G91" s="1">
+        <v>2100083</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I91" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J91" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:10">
+      <c r="C92" s="2">
+        <v>84</v>
+      </c>
+      <c r="D92" s="2">
+        <v>4</v>
+      </c>
+      <c r="E92" s="2">
+        <v>9</v>
+      </c>
+      <c r="F92" s="2">
+        <v>50</v>
+      </c>
+      <c r="G92" s="1">
+        <v>2100084</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I92" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:10">
+      <c r="C93" s="2">
+        <v>85</v>
+      </c>
+      <c r="D93" s="2">
+        <v>4</v>
+      </c>
+      <c r="E93" s="2">
+        <v>8</v>
+      </c>
+      <c r="F93" s="2">
+        <v>50</v>
+      </c>
+      <c r="G93" s="1">
+        <v>2100085</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I93" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:10">
+      <c r="C94" s="2">
+        <v>86</v>
+      </c>
+      <c r="D94" s="2">
+        <v>4</v>
+      </c>
+      <c r="E94" s="2">
+        <v>8</v>
+      </c>
+      <c r="F94" s="2">
+        <v>50</v>
+      </c>
+      <c r="G94" s="1">
+        <v>2100086</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I94" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J94" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:10">
+      <c r="C95" s="2">
+        <v>87</v>
+      </c>
+      <c r="D95" s="2">
+        <v>4</v>
+      </c>
+      <c r="E95" s="2">
+        <v>8</v>
+      </c>
+      <c r="F95" s="2">
+        <v>50</v>
+      </c>
+      <c r="G95" s="1">
+        <v>2100087</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I95" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:10">
+      <c r="C96" s="2">
+        <v>88</v>
+      </c>
+      <c r="D96" s="2">
+        <v>4</v>
+      </c>
+      <c r="E96" s="2">
+        <v>7</v>
+      </c>
+      <c r="F96" s="2">
+        <v>60</v>
+      </c>
+      <c r="G96" s="1">
+        <v>2100088</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I96" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J96" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:10">
+      <c r="C97" s="2">
+        <v>89</v>
+      </c>
+      <c r="D97" s="2">
+        <v>4</v>
+      </c>
+      <c r="E97" s="2">
+        <v>7</v>
+      </c>
+      <c r="F97" s="2">
+        <v>60</v>
+      </c>
+      <c r="G97" s="1">
+        <v>2100089</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I97" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J97" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:10">
+      <c r="C98" s="2">
+        <v>90</v>
+      </c>
+      <c r="D98" s="2">
+        <v>4</v>
+      </c>
+      <c r="E98" s="2">
+        <v>7</v>
+      </c>
+      <c r="F98" s="2">
+        <v>60</v>
+      </c>
+      <c r="G98" s="1">
+        <v>2100090</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I98" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J98" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:10">
+      <c r="C99" s="2">
+        <v>91</v>
+      </c>
+      <c r="D99" s="2">
+        <v>4</v>
+      </c>
+      <c r="E99" s="2">
+        <v>6</v>
+      </c>
+      <c r="F99" s="2">
+        <v>70</v>
+      </c>
+      <c r="G99" s="1">
+        <v>2100091</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="I99" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:10">
+      <c r="C100" s="2">
+        <v>92</v>
+      </c>
+      <c r="D100" s="2">
+        <v>4</v>
+      </c>
+      <c r="E100" s="2">
+        <v>6</v>
+      </c>
+      <c r="F100" s="2">
+        <v>70</v>
+      </c>
+      <c r="G100" s="1">
+        <v>2100092</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I100" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J100" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:10">
+      <c r="C101" s="2">
+        <v>93</v>
+      </c>
+      <c r="D101" s="2">
+        <v>4</v>
+      </c>
+      <c r="E101" s="2">
+        <v>6</v>
+      </c>
+      <c r="F101" s="2">
+        <v>70</v>
+      </c>
+      <c r="G101" s="1">
+        <v>2100093</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I101" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J101" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:10">
+      <c r="C102" s="2">
+        <v>94</v>
+      </c>
+      <c r="D102" s="2">
+        <v>4</v>
+      </c>
+      <c r="E102" s="2">
+        <v>5</v>
+      </c>
+      <c r="F102" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" s="1">
+        <v>2100094</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I102" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J102" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:10">
+      <c r="C103" s="2">
+        <v>95</v>
+      </c>
+      <c r="D103" s="2">
+        <v>4</v>
+      </c>
+      <c r="E103" s="2">
+        <v>5</v>
+      </c>
+      <c r="F103" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" s="1">
+        <v>2100095</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="I103" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J103" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:10">
+      <c r="C104" s="2">
+        <v>96</v>
+      </c>
+      <c r="D104" s="2">
+        <v>4</v>
+      </c>
+      <c r="E104" s="2">
+        <v>5</v>
+      </c>
+      <c r="F104" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" s="1">
+        <v>2100096</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J104" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:10">
+      <c r="C105" s="2">
+        <v>97</v>
+      </c>
+      <c r="D105" s="2">
+        <v>4</v>
+      </c>
+      <c r="E105" s="2">
+        <v>4</v>
+      </c>
+      <c r="F105" s="2">
+        <v>90</v>
+      </c>
+      <c r="G105" s="1">
+        <v>2100097</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I105" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J105" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:10">
+      <c r="C106" s="2">
+        <v>98</v>
+      </c>
+      <c r="D106" s="2">
+        <v>4</v>
+      </c>
+      <c r="E106" s="2">
+        <v>4</v>
+      </c>
+      <c r="F106" s="2">
+        <v>90</v>
+      </c>
+      <c r="G106" s="1">
+        <v>2100098</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I106" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J106" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:10">
+      <c r="C107" s="2">
+        <v>99</v>
+      </c>
+      <c r="D107" s="2">
+        <v>4</v>
+      </c>
+      <c r="E107" s="2">
+        <v>4</v>
+      </c>
+      <c r="F107" s="2">
+        <v>90</v>
+      </c>
+      <c r="G107" s="1">
+        <v>2100099</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I107" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J107" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:10">
+      <c r="C108" s="2">
+        <v>100</v>
+      </c>
+      <c r="D108" s="2">
+        <v>4</v>
+      </c>
+      <c r="E108" s="2">
+        <v>3</v>
+      </c>
+      <c r="F108" s="2">
+        <v>100</v>
+      </c>
+      <c r="G108" s="1">
+        <v>2100100</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I108" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:10">
+      <c r="C109" s="2">
+        <v>101</v>
+      </c>
+      <c r="D109" s="2">
+        <v>4</v>
+      </c>
+      <c r="E109" s="2">
+        <v>3</v>
+      </c>
+      <c r="F109" s="2">
+        <v>100</v>
+      </c>
+      <c r="G109" s="1">
+        <v>2100101</v>
+      </c>
+      <c r="H109" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I109" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J109" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:10">
+      <c r="C110" s="2">
+        <v>102</v>
+      </c>
+      <c r="D110" s="2">
+        <v>4</v>
+      </c>
+      <c r="E110" s="2">
+        <v>3</v>
+      </c>
+      <c r="F110" s="2">
+        <v>100</v>
+      </c>
+      <c r="G110" s="1">
+        <v>2100102</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="I110" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J110" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:10">
+      <c r="C111" s="2">
+        <v>103</v>
+      </c>
+      <c r="D111" s="2">
+        <v>4</v>
+      </c>
+      <c r="E111" s="2">
+        <v>2</v>
+      </c>
+      <c r="F111" s="2">
+        <v>150</v>
+      </c>
+      <c r="G111" s="1">
+        <v>2100103</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="I111" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J111" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:10">
+      <c r="C112" s="2">
+        <v>104</v>
+      </c>
+      <c r="D112" s="2">
+        <v>4</v>
+      </c>
+      <c r="E112" s="2">
+        <v>2</v>
+      </c>
+      <c r="F112" s="2">
+        <v>150</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2100104</v>
+      </c>
+      <c r="H112" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="I112" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J112" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:10">
+      <c r="C113" s="2">
+        <v>105</v>
+      </c>
+      <c r="D113" s="2">
+        <v>4</v>
+      </c>
+      <c r="E113" s="2">
+        <v>2</v>
+      </c>
+      <c r="F113" s="2">
+        <v>150</v>
+      </c>
+      <c r="G113" s="1">
+        <v>2100105</v>
+      </c>
+      <c r="H113" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I113" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J113" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:10">
+      <c r="C114" s="2">
+        <v>106</v>
+      </c>
+      <c r="D114" s="2">
+        <v>4</v>
+      </c>
+      <c r="E114" s="2">
+        <v>1</v>
+      </c>
+      <c r="F114" s="2">
+        <v>200</v>
+      </c>
+      <c r="G114" s="1">
+        <v>2100106</v>
+      </c>
+      <c r="H114" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I114" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J114" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:10">
+      <c r="C115" s="2">
+        <v>107</v>
+      </c>
+      <c r="D115" s="2">
+        <v>4</v>
+      </c>
+      <c r="E115" s="2">
+        <v>1</v>
+      </c>
+      <c r="F115" s="2">
+        <v>200</v>
+      </c>
+      <c r="G115" s="1">
+        <v>2100107</v>
+      </c>
+      <c r="H115" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="I115" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J115" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:10">
+      <c r="C116" s="2">
+        <v>108</v>
+      </c>
+      <c r="D116" s="2">
+        <v>4</v>
+      </c>
+      <c r="E116" s="2">
+        <v>1</v>
+      </c>
+      <c r="F116" s="2">
+        <v>200</v>
+      </c>
+      <c r="G116" s="1">
+        <v>2100108</v>
+      </c>
+      <c r="H116" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I116" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J116" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3832,6 +4662,9 @@
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H115" r:id="rId1" display="马元义" tooltip="https://baike.baidu.com/item/%E9%A9%AC%E5%85%83%E4%B9%89/2282194?fromModule=lemma_inlink"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
